--- a/data/hex_xlsx/YIT.HE.xlsx
+++ b/data/hex_xlsx/YIT.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="562">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1042,6 +1042,9 @@
   </si>
   <si>
     <t>Current liabilities total</t>
+  </si>
+  <si>
+    <t>Bonds LT</t>
   </si>
   <si>
     <t>Loans from financial institution</t>
@@ -1833,7 +1836,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1923,6 +1926,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -18111,8 +18117,8 @@
       </c>
     </row>
     <row r="137" ht="15.0" customHeight="1">
-      <c r="A137" s="14" t="s">
-        <v>325</v>
+      <c r="A137" s="30" t="s">
+        <v>341</v>
       </c>
       <c r="B137" s="21">
         <v>2929.87</v>
@@ -18151,7 +18157,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B138" s="21">
         <v>590.7</v>
@@ -18277,7 +18283,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -18310,7 +18316,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B141" s="20">
         <v>59.07</v>
@@ -18381,7 +18387,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B142" s="20">
         <v>11.81</v>
@@ -18523,7 +18529,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -18552,7 +18558,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -18589,7 +18595,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B146" s="20">
         <v>11.81</v>
@@ -18634,7 +18640,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B147" s="21">
         <v>767.91</v>
@@ -18749,7 +18755,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -18798,7 +18804,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -18831,7 +18837,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -18995,7 +19001,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B156" s="21">
         <v>118.14</v>
@@ -19060,7 +19066,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B157" s="20">
         <v>23.63</v>
@@ -19101,7 +19107,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B158" s="20">
         <v>59.07</v>
@@ -19156,7 +19162,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -19260,7 +19266,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -19297,7 +19303,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -19330,7 +19336,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B163" s="15"/>
       <c r="C163" s="20">
@@ -19371,7 +19377,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B164" s="25">
         <v>7466.45</v>
@@ -19442,7 +19448,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -19473,7 +19479,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -19508,7 +19514,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B167" s="17">
         <v>17780.08</v>
@@ -19579,7 +19585,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B168" s="21">
         <v>1772.1</v>
@@ -19650,7 +19656,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -19713,7 +19719,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B170" s="21">
         <v>6923.01</v>
@@ -19780,7 +19786,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B171" s="21">
         <v>106.33</v>
@@ -19849,7 +19855,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B172" s="18">
         <v>-23.63</v>
@@ -19912,7 +19918,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B173" s="18">
         <v>-82.7</v>
@@ -19981,7 +19987,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B174" s="19">
         <v>-1051.45</v>
@@ -20050,7 +20056,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -20079,7 +20085,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -20108,7 +20114,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -20143,7 +20149,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -20172,7 +20178,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B179" s="20">
         <v>11.81</v>
@@ -20203,7 +20209,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B180" s="15"/>
       <c r="C180" s="18">
@@ -20246,7 +20252,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B181" s="25">
         <v>7643.66</v>
@@ -20372,7 +20378,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B183" s="21">
         <v>1701.22</v>
@@ -20409,7 +20415,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B184" s="25">
         <v>1701.22</v>
@@ -20470,7 +20476,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B185" s="25">
         <v>9356.69</v>
@@ -20541,7 +20547,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B186" s="18">
         <v>-11.81</v>
@@ -20576,7 +20582,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B187" s="17">
         <v>27124.96</v>
@@ -20647,7 +20653,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B188" s="21">
         <v>230.65</v>
@@ -20718,7 +20724,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B189" s="20">
         <v>1.41</v>
@@ -20789,7 +20795,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B190" s="21">
         <v>232.06</v>
@@ -20860,7 +20866,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -20913,7 +20919,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -20968,7 +20974,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B193" s="15"/>
       <c r="C193" s="21">
@@ -20997,7 +21003,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B194" s="21">
         <v>1559.45</v>
@@ -21054,7 +21060,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B195" s="21">
         <v>2008.38</v>
@@ -21111,7 +21117,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B196" s="21">
         <v>437.12</v>
@@ -21168,7 +21174,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B197" s="15">
         <v>0.0</v>
@@ -21233,7 +21239,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B198" s="15">
         <v>0.0</v>
@@ -21296,7 +21302,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B199" s="21">
         <v>366.23</v>
@@ -21363,7 +21369,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B200" s="21">
         <v>342.61</v>
@@ -21410,7 +21416,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B201" s="21">
         <v>271.72</v>
@@ -21457,7 +21463,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B202" s="21">
         <v>224.47</v>
@@ -21502,7 +21508,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B203" s="21">
         <v>177.21</v>
@@ -21559,7 +21565,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B204" s="21">
         <v>5174.54</v>
@@ -21612,7 +21618,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -21675,7 +21681,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -21712,7 +21718,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B207" s="21">
         <v>1890.24</v>
@@ -21747,7 +21753,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B208" s="21">
         <v>472.56</v>
@@ -21778,7 +21784,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B209" s="21">
         <v>2362.8</v>
@@ -21815,7 +21821,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B210" s="21">
         <v>230.65</v>
@@ -21886,7 +21892,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B211" s="20">
         <v>1.41</v>
@@ -21925,7 +21931,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B212" s="20">
         <v>1.0</v>
@@ -21996,7 +22002,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B213" s="21">
         <v>232.06</v>
@@ -22873,7 +22879,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23259,70 +23265,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -23398,7 +23404,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -23567,7 +23573,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -23606,7 +23612,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -23712,7 +23718,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B24" s="15">
         <v>0.0</v>
@@ -23775,7 +23781,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B25" s="21">
         <v>643.64</v>
@@ -23838,7 +23844,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -23875,7 +23881,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B27" s="21">
         <v>163.84</v>
@@ -23942,7 +23948,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -23977,7 +23983,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -24006,7 +24012,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B30" s="19">
         <v>-175.54</v>
@@ -24057,7 +24063,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -24092,7 +24098,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -24125,7 +24131,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B33" s="21">
         <v>479.81</v>
@@ -24182,7 +24188,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B34" s="20">
         <v>93.62</v>
@@ -24253,7 +24259,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B35" s="21">
         <v>1053.23</v>
@@ -24324,7 +24330,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B36" s="19">
         <v>-655.34</v>
@@ -24395,7 +24401,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -24424,7 +24430,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B38" s="19">
         <v>-737.26</v>
@@ -24495,7 +24501,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B39" s="19">
         <v>-140.43</v>
@@ -24548,7 +24554,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B40" s="20">
         <v>70.22</v>
@@ -24619,7 +24625,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -24670,7 +24676,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B42" s="19">
         <v>-105.32</v>
@@ -24741,7 +24747,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -24780,7 +24786,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -24821,7 +24827,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -24850,7 +24856,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -24885,7 +24891,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -24918,7 +24924,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -24955,7 +24961,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="18">
@@ -24992,7 +24998,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B50" s="25">
         <v>152.13</v>
@@ -25063,7 +25069,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B51" s="18">
         <v>-23.41</v>
@@ -25132,7 +25138,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B52" s="20">
         <v>58.51</v>
@@ -25169,7 +25175,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -25198,7 +25204,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -25229,7 +25235,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -25270,7 +25276,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B56" s="20">
         <v>35.11</v>
@@ -25305,7 +25311,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -25336,7 +25342,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B58" s="20">
         <v>58.51</v>
@@ -25371,7 +25377,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -25400,7 +25406,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B60" s="18">
         <v>-35.11</v>
@@ -25471,7 +25477,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15">
@@ -25518,7 +25524,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -25579,7 +25585,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -25610,7 +25616,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -25647,7 +25653,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -25690,7 +25696,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -25741,7 +25747,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -25776,7 +25782,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B68" s="19">
         <v>-374.48</v>
@@ -25809,7 +25815,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -25852,7 +25858,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" s="20">
         <v>23.41</v>
@@ -25926,7 +25932,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B72" s="21">
         <v>631.94</v>
@@ -25955,7 +25961,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B73" s="21">
         <v>245.75</v>
@@ -25992,7 +25998,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B74" s="18">
         <v>-11.7</v>
@@ -26037,7 +26043,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B75" s="25">
         <v>608.53</v>
@@ -26108,7 +26114,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -26143,7 +26149,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -26210,7 +26216,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B78" s="19">
         <v>-1568.14</v>
@@ -26267,7 +26273,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B79" s="21">
         <v>3393.75</v>
@@ -26308,7 +26314,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -26365,7 +26371,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B81" s="19">
         <v>-4095.9</v>
@@ -26406,7 +26412,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B82" s="19">
         <v>-210.65</v>
@@ -26473,7 +26479,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15">
@@ -26542,7 +26548,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B84" s="15">
         <v>0.0</v>
@@ -26583,7 +26589,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -26640,7 +26646,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -26671,7 +26677,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B87" s="21">
         <v>924.5</v>
@@ -26712,7 +26718,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B88" s="21">
         <v>1170.26</v>
@@ -26743,7 +26749,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -26784,7 +26790,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -26815,7 +26821,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -26850,7 +26856,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -26887,7 +26893,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B93" s="19">
         <v>-631.94</v>
@@ -26916,7 +26922,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B94" s="24">
         <v>-1018.12</v>
@@ -26987,7 +26993,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -27016,7 +27022,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="16" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -27045,7 +27051,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B97" s="19">
         <v>-257.46</v>
@@ -27100,7 +27106,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B98" s="21">
         <v>1618.52</v>
@@ -27171,7 +27177,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B99" s="20">
         <v>11.7</v>
@@ -27240,7 +27246,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B100" s="21">
         <v>1370.42</v>
@@ -27311,7 +27317,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -27340,7 +27346,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -27369,7 +27375,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -27400,7 +27406,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="16" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B104" s="24">
         <v>-245.75</v>
@@ -27471,7 +27477,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -27500,7 +27506,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -28442,7 +28448,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -28619,31 +28625,31 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -29132,7 +29138,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -29237,3856 +29243,3856 @@
         <v>70</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>510</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-      <c r="AE20" s="31"/>
-      <c r="AF20" s="31"/>
+      <c r="A20" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="32" t="s">
-        <v>510</v>
-      </c>
-      <c r="B21" s="33">
+      <c r="A21" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="B21" s="34">
         <v>17915.83</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>16860.03</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <v>15525.21</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>12007.69</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>12771.49</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>18209.12</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <v>21421.55</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <v>16900.16</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <v>12625.63</v>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="34">
         <v>14201.89</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="34">
         <v>11243.63</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="34">
         <v>11027.85</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="34">
         <v>16912.11</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>15781.66</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>12306.14</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="34">
         <v>17328.36</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="34">
         <v>14898.98</v>
       </c>
-      <c r="S21" s="34">
+      <c r="S21" s="35">
         <v>8863.13</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="34">
         <v>14258.78</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="34">
         <v>18907.41</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="34">
         <v>14471.94</v>
       </c>
-      <c r="W21" s="34">
+      <c r="W21" s="35">
         <v>8687.84</v>
       </c>
-      <c r="X21" s="34">
+      <c r="X21" s="35">
         <v>8616.23</v>
       </c>
-      <c r="Y21" s="34">
+      <c r="Y21" s="35">
         <v>4672.28</v>
       </c>
-      <c r="Z21" s="34">
+      <c r="Z21" s="35">
         <v>4119.22</v>
       </c>
-      <c r="AA21" s="34">
+      <c r="AA21" s="35">
         <v>4388.31</v>
       </c>
-      <c r="AB21" s="34">
+      <c r="AB21" s="35">
         <v>3599.85</v>
       </c>
-      <c r="AC21" s="34">
+      <c r="AC21" s="35">
         <v>3317.06</v>
       </c>
-      <c r="AD21" s="34">
+      <c r="AD21" s="35">
         <v>3398.31</v>
       </c>
-      <c r="AE21" s="34">
+      <c r="AE21" s="35">
         <v>3298.6</v>
       </c>
-      <c r="AF21" s="34">
+      <c r="AF21" s="35">
         <v>2867.97</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="32" t="s">
-        <v>511</v>
-      </c>
-      <c r="B22" s="33">
+      <c r="A22" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="B22" s="34">
         <v>15968.62</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="34">
         <v>16426.66</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <v>17278.7</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <v>16862.38</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <v>16376.53</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <v>17740.9</v>
       </c>
-      <c r="H22" s="33">
+      <c r="H22" s="34">
         <v>15548.76</v>
       </c>
-      <c r="I22" s="33">
+      <c r="I22" s="34">
         <v>13758.8</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="34">
         <v>14307.02</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="34">
         <v>14771.07</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="34">
         <v>15667.83</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="34">
         <v>16657.14</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="34">
         <v>16326.83</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <v>12734.84</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="34">
         <v>12879.14</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="34">
         <v>14067.38</v>
       </c>
-      <c r="R22" s="33">
+      <c r="R22" s="34">
         <v>14297.09</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="34">
         <v>15294.88</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="34">
         <v>12671.36</v>
       </c>
-      <c r="U22" s="33">
+      <c r="U22" s="34">
         <v>11243.18</v>
       </c>
-      <c r="V22" s="34">
+      <c r="V22" s="35">
         <v>8069.39</v>
       </c>
-      <c r="W22" s="34">
+      <c r="W22" s="35">
         <v>6214.47</v>
       </c>
-      <c r="X22" s="34">
+      <c r="X22" s="35">
         <v>5310.54</v>
       </c>
-      <c r="Y22" s="34">
+      <c r="Y22" s="35">
         <v>3647.32</v>
       </c>
-      <c r="Z22" s="34">
+      <c r="Z22" s="35">
         <v>3639.83</v>
       </c>
-      <c r="AA22" s="34">
+      <c r="AA22" s="35">
         <v>3595.79</v>
       </c>
-      <c r="AB22" s="34">
+      <c r="AB22" s="35">
         <v>3227.05</v>
       </c>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>512</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="31"/>
-      <c r="AF23" s="31"/>
+      <c r="A23" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="32" t="s">
-        <v>512</v>
-      </c>
-      <c r="B24" s="34">
+      <c r="A24" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="B24" s="35">
         <v>8559.14</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="35">
         <v>6799.29</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="35">
         <v>4686.9</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="35">
         <v>5444.54</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="35">
         <v>9117.3</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <v>10907.22</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <v>12380.99</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <v>10677.15</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="35">
         <v>7692.24</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="35">
         <v>8453.27</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="35">
         <v>6164.26</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="35">
         <v>4734.07</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>10390.89</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>10279.72</v>
       </c>
-      <c r="P24" s="34">
+      <c r="P24" s="35">
         <v>9076.06</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>13763.13</v>
       </c>
-      <c r="R24" s="33">
+      <c r="R24" s="34">
         <v>11356.48</v>
       </c>
-      <c r="S24" s="34">
+      <c r="S24" s="35">
         <v>4213.3</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="34">
         <v>11261.69</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="34">
         <v>16270.53</v>
       </c>
-      <c r="V24" s="33">
+      <c r="V24" s="34">
         <v>13406.88</v>
       </c>
-      <c r="W24" s="34">
+      <c r="W24" s="35">
         <v>6904.8</v>
       </c>
-      <c r="X24" s="34">
+      <c r="X24" s="35">
         <v>5133.45</v>
       </c>
-      <c r="Y24" s="34">
+      <c r="Y24" s="35">
         <v>2705.22</v>
       </c>
-      <c r="Z24" s="34">
+      <c r="Z24" s="35">
         <v>2353.44</v>
       </c>
-      <c r="AA24" s="34">
+      <c r="AA24" s="35">
         <v>2458.99</v>
       </c>
-      <c r="AB24" s="34">
+      <c r="AB24" s="35">
         <v>1925.42</v>
       </c>
-      <c r="AC24" s="34">
+      <c r="AC24" s="35">
         <v>1446.16</v>
       </c>
-      <c r="AD24" s="34">
+      <c r="AD24" s="35">
         <v>1828.65</v>
       </c>
-      <c r="AE24" s="34">
+      <c r="AE24" s="35">
         <v>1331.21</v>
       </c>
-      <c r="AF24" s="34">
+      <c r="AF24" s="35">
         <v>768.28</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="32" t="s">
-        <v>513</v>
-      </c>
-      <c r="B25" s="34">
+      <c r="A25" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B25" s="35">
         <v>7446.0</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="35">
         <v>8161.55</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="35">
         <v>9279.83</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <v>10079.48</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <v>10149.59</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="34">
         <v>10663.19</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="35">
         <v>9230.91</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="35">
         <v>7838.57</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="35">
         <v>8120.93</v>
       </c>
-      <c r="K25" s="34">
+      <c r="K25" s="35">
         <v>8614.4</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="35">
         <v>9572.58</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>11047.07</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>11600.6</v>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="35">
         <v>9019.45</v>
       </c>
-      <c r="P25" s="34">
+      <c r="P25" s="35">
         <v>9537.84</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="34">
         <v>10854.92</v>
       </c>
-      <c r="R25" s="33">
+      <c r="R25" s="34">
         <v>11414.01</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="34">
         <v>12329.22</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="34">
         <v>10350.87</v>
       </c>
-      <c r="U25" s="34">
+      <c r="U25" s="35">
         <v>9012.88</v>
       </c>
-      <c r="V25" s="34">
+      <c r="V25" s="35">
         <v>6062.26</v>
       </c>
-      <c r="W25" s="34">
+      <c r="W25" s="35">
         <v>3978.62</v>
       </c>
-      <c r="X25" s="34">
+      <c r="X25" s="35">
         <v>3047.39</v>
       </c>
-      <c r="Y25" s="34">
+      <c r="Y25" s="35">
         <v>1985.83</v>
       </c>
-      <c r="Z25" s="34">
+      <c r="Z25" s="35">
         <v>1942.16</v>
       </c>
-      <c r="AA25" s="34">
+      <c r="AA25" s="35">
         <v>1798.63</v>
       </c>
-      <c r="AB25" s="34">
+      <c r="AB25" s="35">
         <v>1429.83</v>
       </c>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="33"/>
-      <c r="AE25" s="33"/>
-      <c r="AF25" s="33"/>
+      <c r="AC25" s="34"/>
+      <c r="AD25" s="34"/>
+      <c r="AE25" s="34"/>
+      <c r="AF25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>514</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
+      <c r="A26" s="31" t="s">
+        <v>515</v>
+      </c>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="32" t="s">
-        <v>515</v>
-      </c>
-      <c r="B27" s="35">
+      <c r="A27" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="B27" s="36">
         <v>36.88</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="36">
         <v>29.3</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="36">
         <v>22.2</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="36">
         <v>25.79</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="36">
         <v>43.19</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="36">
         <v>51.67</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="36">
         <v>58.65</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="36">
         <v>50.58</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="36">
         <v>60.46</v>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="36">
         <v>66.44</v>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="36">
         <v>48.45</v>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="36">
         <v>37.21</v>
       </c>
-      <c r="N27" s="35">
+      <c r="N27" s="36">
         <v>81.67</v>
       </c>
-      <c r="O27" s="35">
+      <c r="O27" s="36">
         <v>80.8</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="36">
         <v>71.34</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>108.18</v>
       </c>
-      <c r="R27" s="35">
+      <c r="R27" s="36">
         <v>89.26</v>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="36">
         <v>33.12</v>
       </c>
-      <c r="T27" s="35">
+      <c r="T27" s="36">
         <v>88.52</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>128.34</v>
       </c>
-      <c r="V27" s="34">
+      <c r="V27" s="35">
         <v>107.43</v>
       </c>
-      <c r="W27" s="35">
+      <c r="W27" s="36">
         <v>56.33</v>
       </c>
-      <c r="X27" s="35">
+      <c r="X27" s="36">
         <v>42.05</v>
       </c>
-      <c r="Y27" s="35">
+      <c r="Y27" s="36">
         <v>22.74</v>
       </c>
-      <c r="Z27" s="35">
+      <c r="Z27" s="36">
         <v>20.02</v>
       </c>
-      <c r="AA27" s="35">
+      <c r="AA27" s="36">
         <v>20.92</v>
       </c>
-      <c r="AB27" s="35">
+      <c r="AB27" s="36">
         <v>16.38</v>
       </c>
-      <c r="AC27" s="35">
+      <c r="AC27" s="36">
         <v>12.32</v>
       </c>
-      <c r="AD27" s="35">
+      <c r="AD27" s="36">
         <v>15.6</v>
       </c>
-      <c r="AE27" s="35">
+      <c r="AE27" s="36">
         <v>13.63</v>
       </c>
-      <c r="AF27" s="35">
+      <c r="AF27" s="36">
         <v>7.86</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="32" t="s">
-        <v>516</v>
-      </c>
-      <c r="B28" s="35">
+      <c r="A28" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="B28" s="36">
         <v>33.96</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="36">
         <v>38.08</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="36">
         <v>43.96</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="36">
         <v>47.75</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="36">
         <v>52.97</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="36">
         <v>61.72</v>
       </c>
-      <c r="H28" s="35">
+      <c r="H28" s="36">
         <v>58.2</v>
       </c>
-      <c r="I28" s="35">
+      <c r="I28" s="36">
         <v>54.94</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="36">
         <v>63.83</v>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="36">
         <v>67.71</v>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="36">
         <v>75.24</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="36">
         <v>86.83</v>
       </c>
-      <c r="N28" s="35">
+      <c r="N28" s="36">
         <v>91.18</v>
       </c>
-      <c r="O28" s="35">
+      <c r="O28" s="36">
         <v>70.89</v>
       </c>
-      <c r="P28" s="35">
+      <c r="P28" s="36">
         <v>74.97</v>
       </c>
-      <c r="Q28" s="35">
+      <c r="Q28" s="36">
         <v>85.41</v>
       </c>
-      <c r="R28" s="35">
+      <c r="R28" s="36">
         <v>90.23</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="36">
         <v>98.0</v>
       </c>
-      <c r="T28" s="35">
+      <c r="T28" s="36">
         <v>82.57</v>
       </c>
-      <c r="U28" s="35">
+      <c r="U28" s="36">
         <v>72.43</v>
       </c>
-      <c r="V28" s="35">
+      <c r="V28" s="36">
         <v>49.41</v>
       </c>
-      <c r="W28" s="35">
+      <c r="W28" s="36">
         <v>32.98</v>
       </c>
-      <c r="X28" s="35">
+      <c r="X28" s="36">
         <v>25.54</v>
       </c>
-      <c r="Y28" s="35">
+      <c r="Y28" s="36">
         <v>16.84</v>
       </c>
-      <c r="Z28" s="35">
+      <c r="Z28" s="36">
         <v>16.54</v>
       </c>
-      <c r="AA28" s="35">
+      <c r="AA28" s="36">
         <v>15.79</v>
       </c>
-      <c r="AB28" s="35">
+      <c r="AB28" s="36">
         <v>12.9</v>
       </c>
-      <c r="AC28" s="33"/>
-      <c r="AD28" s="33"/>
-      <c r="AE28" s="33"/>
-      <c r="AF28" s="33"/>
+      <c r="AC28" s="34"/>
+      <c r="AD28" s="34"/>
+      <c r="AE28" s="34"/>
+      <c r="AF28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
+      <c r="A29" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="32" t="s">
-        <v>518</v>
-      </c>
-      <c r="B30" s="36">
+      <c r="A30" s="33" t="s">
+        <v>519</v>
+      </c>
+      <c r="B30" s="37">
         <v>1.39</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>9.4</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="38">
         <v>-34.37</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="38">
         <v>-55.91</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>29.43</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>3.98</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>4.0</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>13.7</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>28.08</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>1.85</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>28.78</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="37">
         <v>28.57</v>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="38">
         <v>-8.76</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="37">
         <v>3.12</v>
       </c>
-      <c r="P30" s="37">
+      <c r="P30" s="38">
         <v>-1.87</v>
       </c>
-      <c r="Q30" s="37">
+      <c r="Q30" s="38">
         <v>-1.23</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>17.29</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="37">
         <v>2.34</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="37">
         <v>3.45</v>
       </c>
-      <c r="U30" s="37">
+      <c r="U30" s="38">
         <v>-9.36</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>8.25</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>4.11</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="38">
         <v>-22.39</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>4.51</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="38">
         <v>-9.0</v>
       </c>
-      <c r="AA30" s="36">
+      <c r="AA30" s="37">
         <v>5.11</v>
       </c>
-      <c r="AB30" s="36">
+      <c r="AB30" s="37">
         <v>13.06</v>
       </c>
-      <c r="AC30" s="36">
+      <c r="AC30" s="37">
         <v>10.57</v>
       </c>
-      <c r="AD30" s="37">
+      <c r="AD30" s="38">
         <v>-4.8</v>
       </c>
-      <c r="AE30" s="36">
+      <c r="AE30" s="37">
         <v>17.39</v>
       </c>
-      <c r="AF30" s="37">
+      <c r="AF30" s="38">
         <v>-170.33</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="32" t="s">
-        <v>519</v>
-      </c>
-      <c r="B31" s="37">
+      <c r="A31" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="B31" s="38">
         <v>-3.56</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="38">
         <v>-2.21</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="38">
         <v>-1.8</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="37">
         <v>4.51</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>15.61</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>10.16</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>14.37</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>18.71</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>11.2</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>6.03</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <v>4.95</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>0.66</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>1.83</v>
       </c>
-      <c r="O31" s="36">
+      <c r="O31" s="37">
         <v>4.02</v>
       </c>
-      <c r="P31" s="36">
+      <c r="P31" s="37">
         <v>4.09</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="Q31" s="37">
         <v>1.26</v>
       </c>
-      <c r="R31" s="36">
+      <c r="R31" s="37">
         <v>3.63</v>
       </c>
-      <c r="S31" s="36">
+      <c r="S31" s="37">
         <v>0.78</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="38">
         <v>-1.55</v>
       </c>
-      <c r="U31" s="37">
+      <c r="U31" s="38">
         <v>-2.39</v>
       </c>
-      <c r="V31" s="36">
+      <c r="V31" s="37">
         <v>0.59</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="38">
         <v>-3.98</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="38">
         <v>-5.34</v>
       </c>
-      <c r="Y31" s="36">
+      <c r="Y31" s="37">
         <v>3.93</v>
       </c>
-      <c r="Z31" s="36">
+      <c r="Z31" s="37">
         <v>2.13</v>
       </c>
-      <c r="AA31" s="36">
+      <c r="AA31" s="37">
         <v>7.76</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="38">
         <v>-13.03</v>
       </c>
-      <c r="AC31" s="36"/>
-      <c r="AD31" s="36"/>
-      <c r="AE31" s="36"/>
-      <c r="AF31" s="36"/>
+      <c r="AC31" s="37"/>
+      <c r="AD31" s="37"/>
+      <c r="AE31" s="37"/>
+      <c r="AF31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>520</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
+      <c r="A32" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="32" t="s">
-        <v>521</v>
-      </c>
-      <c r="B33" s="36">
+      <c r="A33" s="33" t="s">
+        <v>522</v>
+      </c>
+      <c r="B33" s="37">
         <v>0.0</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>0.0</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>9.07</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>6.5</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>3.25</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>8.11</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>4.53</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="37">
         <v>0.0</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <v>3.58</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <v>3.01</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <v>3.57</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <v>9.23</v>
       </c>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36">
+      <c r="N33" s="37"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="37">
         <v>5.67</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="Q33" s="37">
         <v>2.32</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="37">
         <v>3.74</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="37">
         <v>18.85</v>
       </c>
-      <c r="T33" s="36">
+      <c r="T33" s="37">
         <v>4.68</v>
       </c>
-      <c r="U33" s="36">
+      <c r="U33" s="37">
         <v>2.83</v>
       </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36">
+      <c r="V33" s="37"/>
+      <c r="W33" s="37">
         <v>2.56</v>
       </c>
-      <c r="X33" s="36">
+      <c r="X33" s="37">
         <v>4.49</v>
       </c>
-      <c r="Y33" s="36">
+      <c r="Y33" s="37">
         <v>6.8</v>
       </c>
-      <c r="Z33" s="36">
+      <c r="Z33" s="37">
         <v>7.46</v>
       </c>
-      <c r="AA33" s="36">
+      <c r="AA33" s="37">
         <v>5.92</v>
       </c>
-      <c r="AB33" s="36">
+      <c r="AB33" s="37">
         <v>5.17</v>
       </c>
-      <c r="AC33" s="36">
+      <c r="AC33" s="37">
         <v>6.1</v>
       </c>
-      <c r="AD33" s="36">
+      <c r="AD33" s="37">
         <v>3.27</v>
       </c>
-      <c r="AE33" s="36">
+      <c r="AE33" s="37">
         <v>1.25</v>
       </c>
-      <c r="AF33" s="36">
+      <c r="AF33" s="37">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="32" t="s">
-        <v>522</v>
-      </c>
-      <c r="B34" s="36">
+      <c r="A34" s="33" t="s">
+        <v>523</v>
+      </c>
+      <c r="B34" s="37">
         <v>3.34</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>5.44</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>5.85</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="37">
         <v>4.26</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="37">
         <v>3.89</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="37">
         <v>3.77</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <v>3.01</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="37">
         <v>3.61</v>
       </c>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36">
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37">
         <v>4.98</v>
       </c>
-      <c r="Q34" s="36">
+      <c r="Q34" s="37">
         <v>4.25</v>
       </c>
-      <c r="R34" s="36"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36">
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="37">
         <v>4.75</v>
       </c>
-      <c r="X34" s="36">
+      <c r="X34" s="37">
         <v>5.79</v>
       </c>
-      <c r="Y34" s="36">
+      <c r="Y34" s="37">
         <v>6.38</v>
       </c>
-      <c r="Z34" s="36">
+      <c r="Z34" s="37">
         <v>5.68</v>
       </c>
-      <c r="AA34" s="36">
+      <c r="AA34" s="37">
         <v>4.43</v>
       </c>
-      <c r="AB34" s="36">
+      <c r="AB34" s="37">
         <v>3.42</v>
       </c>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
-      <c r="AE34" s="36"/>
-      <c r="AF34" s="36"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="37"/>
+      <c r="AE34" s="37"/>
+      <c r="AF34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="32" t="s">
-        <v>523</v>
-      </c>
-      <c r="B35" s="36">
+      <c r="A35" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="B35" s="37">
         <v>0.0</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>0.0</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>9.07</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>6.5</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>3.25</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>8.11</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>4.53</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>0.0</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <v>3.58</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <v>3.01</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <v>3.57</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>9.23</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>7.66</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>6.36</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>7.05</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="Q35" s="37">
         <v>2.88</v>
       </c>
-      <c r="R35" s="36">
+      <c r="R35" s="37">
         <v>4.65</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="37">
         <v>23.45</v>
       </c>
-      <c r="T35" s="36">
+      <c r="T35" s="37">
         <v>5.82</v>
       </c>
-      <c r="U35" s="36">
+      <c r="U35" s="37">
         <v>3.52</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>2.6</v>
       </c>
-      <c r="W35" s="36">
+      <c r="W35" s="37">
         <v>4.39</v>
       </c>
-      <c r="X35" s="36">
+      <c r="X35" s="37">
         <v>4.49</v>
       </c>
-      <c r="Y35" s="36">
+      <c r="Y35" s="37">
         <v>6.8</v>
       </c>
-      <c r="Z35" s="36">
+      <c r="Z35" s="37">
         <v>7.46</v>
       </c>
-      <c r="AA35" s="36">
+      <c r="AA35" s="37">
         <v>5.92</v>
       </c>
-      <c r="AB35" s="36">
+      <c r="AB35" s="37">
         <v>5.17</v>
       </c>
-      <c r="AC35" s="36">
+      <c r="AC35" s="37">
         <v>6.1</v>
       </c>
-      <c r="AD35" s="36">
+      <c r="AD35" s="37">
         <v>3.27</v>
       </c>
-      <c r="AE35" s="36">
+      <c r="AE35" s="37">
         <v>1.25</v>
       </c>
-      <c r="AF35" s="36">
+      <c r="AF35" s="37">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="32" t="s">
-        <v>524</v>
-      </c>
-      <c r="B36" s="36">
+      <c r="A36" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="B36" s="37">
         <v>3.34</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>5.44</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>5.85</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="37">
         <v>4.26</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="37">
         <v>3.89</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="37">
         <v>3.77</v>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <v>3.01</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>3.61</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <v>5.4</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <v>5.98</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <v>6.79</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <v>6.0</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <v>5.49</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="37">
         <v>6.32</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="37">
         <v>6.19</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="Q36" s="37">
         <v>5.29</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="37">
         <v>5.24</v>
       </c>
-      <c r="S36" s="36">
+      <c r="S36" s="37">
         <v>5.25</v>
       </c>
-      <c r="T36" s="36">
+      <c r="T36" s="37">
         <v>3.98</v>
       </c>
-      <c r="U36" s="36">
+      <c r="U36" s="37">
         <v>3.72</v>
       </c>
-      <c r="V36" s="36">
+      <c r="V36" s="37">
         <v>4.12</v>
       </c>
-      <c r="W36" s="36">
+      <c r="W36" s="37">
         <v>5.37</v>
       </c>
-      <c r="X36" s="36">
+      <c r="X36" s="37">
         <v>5.79</v>
       </c>
-      <c r="Y36" s="36">
+      <c r="Y36" s="37">
         <v>6.38</v>
       </c>
-      <c r="Z36" s="36">
+      <c r="Z36" s="37">
         <v>5.68</v>
       </c>
-      <c r="AA36" s="36">
+      <c r="AA36" s="37">
         <v>4.43</v>
       </c>
-      <c r="AB36" s="36">
+      <c r="AB36" s="37">
         <v>3.42</v>
       </c>
-      <c r="AC36" s="36"/>
-      <c r="AD36" s="36"/>
-      <c r="AE36" s="36"/>
-      <c r="AF36" s="36"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
+      <c r="AE36" s="37"/>
+      <c r="AF36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>525</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="31"/>
-      <c r="Y37" s="31"/>
-      <c r="Z37" s="31"/>
-      <c r="AA37" s="31"/>
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
+      <c r="A37" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+      <c r="Z37" s="32"/>
+      <c r="AA37" s="32"/>
+      <c r="AB37" s="32"/>
+      <c r="AC37" s="32"/>
+      <c r="AD37" s="32"/>
+      <c r="AE37" s="32"/>
+      <c r="AF37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="32" t="s">
-        <v>526</v>
-      </c>
-      <c r="B38" s="35">
+      <c r="A38" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="B38" s="36">
         <v>1.11</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="36">
         <v>0.86</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="36">
         <v>0.56</v>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="36">
         <v>0.66</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="36">
         <v>0.99</v>
       </c>
-      <c r="G38" s="35">
+      <c r="G38" s="36">
         <v>1.12</v>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="36">
         <v>1.17</v>
       </c>
-      <c r="I38" s="35">
+      <c r="I38" s="36">
         <v>1.02</v>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="36">
         <v>1.37</v>
       </c>
-      <c r="K38" s="35">
+      <c r="K38" s="36">
         <v>1.63</v>
       </c>
-      <c r="L38" s="35">
+      <c r="L38" s="36">
         <v>1.21</v>
       </c>
-      <c r="M38" s="35">
+      <c r="M38" s="36">
         <v>0.97</v>
       </c>
-      <c r="N38" s="35">
+      <c r="N38" s="36">
         <v>1.78</v>
       </c>
-      <c r="O38" s="35">
+      <c r="O38" s="36">
         <v>1.37</v>
       </c>
-      <c r="P38" s="35">
+      <c r="P38" s="36">
         <v>1.26</v>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="36">
         <v>1.97</v>
       </c>
-      <c r="R38" s="35">
+      <c r="R38" s="36">
         <v>1.77</v>
       </c>
-      <c r="S38" s="35">
+      <c r="S38" s="36">
         <v>0.53</v>
       </c>
-      <c r="T38" s="35">
+      <c r="T38" s="36">
         <v>1.74</v>
       </c>
-      <c r="U38" s="35">
+      <c r="U38" s="36">
         <v>2.95</v>
       </c>
-      <c r="V38" s="35">
+      <c r="V38" s="36">
         <v>3.0</v>
       </c>
-      <c r="W38" s="35">
+      <c r="W38" s="36">
         <v>1.9</v>
       </c>
-      <c r="X38" s="35">
+      <c r="X38" s="36">
         <v>1.5</v>
       </c>
-      <c r="Y38" s="35">
+      <c r="Y38" s="36">
         <v>1.0</v>
       </c>
-      <c r="Z38" s="35">
+      <c r="Z38" s="36">
         <v>0.84</v>
       </c>
-      <c r="AA38" s="35">
+      <c r="AA38" s="36">
         <v>0.94</v>
       </c>
-      <c r="AB38" s="35">
+      <c r="AB38" s="36">
         <v>0.89</v>
       </c>
-      <c r="AC38" s="35">
+      <c r="AC38" s="36">
         <v>0.04</v>
       </c>
-      <c r="AD38" s="35">
+      <c r="AD38" s="36">
         <v>1.09</v>
       </c>
-      <c r="AE38" s="35">
+      <c r="AE38" s="36">
         <v>1.83</v>
       </c>
-      <c r="AF38" s="35">
+      <c r="AF38" s="36">
         <v>1.34</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="32" t="s">
-        <v>527</v>
-      </c>
-      <c r="B39" s="35">
+      <c r="A39" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="B39" s="36">
         <v>0.83</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <v>0.85</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="36">
         <v>0.93</v>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="36">
         <v>1.01</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="36">
         <v>1.13</v>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="36">
         <v>1.26</v>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="36">
         <v>1.27</v>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="36">
         <v>1.24</v>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="36">
         <v>1.42</v>
       </c>
-      <c r="K39" s="35">
+      <c r="K39" s="36">
         <v>1.41</v>
       </c>
-      <c r="L39" s="35">
+      <c r="L39" s="36">
         <v>1.34</v>
       </c>
-      <c r="M39" s="35">
+      <c r="M39" s="36">
         <v>1.49</v>
       </c>
-      <c r="N39" s="35">
+      <c r="N39" s="36">
         <v>1.61</v>
       </c>
-      <c r="O39" s="35">
+      <c r="O39" s="36">
         <v>1.39</v>
       </c>
-      <c r="P39" s="35">
+      <c r="P39" s="36">
         <v>1.46</v>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="36">
         <v>1.76</v>
       </c>
-      <c r="R39" s="35">
+      <c r="R39" s="36">
         <v>1.9</v>
       </c>
-      <c r="S39" s="35">
+      <c r="S39" s="36">
         <v>1.93</v>
       </c>
-      <c r="T39" s="35">
+      <c r="T39" s="36">
         <v>2.25</v>
       </c>
-      <c r="U39" s="35">
+      <c r="U39" s="36">
         <v>2.22</v>
       </c>
-      <c r="V39" s="35">
+      <c r="V39" s="36">
         <v>1.76</v>
       </c>
-      <c r="W39" s="35">
+      <c r="W39" s="36">
         <v>1.27</v>
       </c>
-      <c r="X39" s="35">
+      <c r="X39" s="36">
         <v>1.05</v>
       </c>
-      <c r="Y39" s="35">
+      <c r="Y39" s="36">
         <v>0.28</v>
       </c>
-      <c r="Z39" s="35">
+      <c r="Z39" s="36">
         <v>0.26</v>
       </c>
-      <c r="AA39" s="35">
+      <c r="AA39" s="36">
         <v>0.25</v>
       </c>
-      <c r="AB39" s="35">
+      <c r="AB39" s="36">
         <v>0.22</v>
       </c>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="33"/>
-      <c r="AE39" s="33"/>
-      <c r="AF39" s="33"/>
+      <c r="AC39" s="34"/>
+      <c r="AD39" s="34"/>
+      <c r="AE39" s="34"/>
+      <c r="AF39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="30" t="s">
-        <v>528</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="31"/>
-      <c r="W40" s="31"/>
-      <c r="X40" s="31"/>
-      <c r="Y40" s="31"/>
-      <c r="Z40" s="31"/>
-      <c r="AA40" s="31"/>
-      <c r="AB40" s="31"/>
-      <c r="AC40" s="31"/>
-      <c r="AD40" s="31"/>
-      <c r="AE40" s="31"/>
-      <c r="AF40" s="31"/>
+      <c r="A40" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="32"/>
+      <c r="W40" s="32"/>
+      <c r="X40" s="32"/>
+      <c r="Y40" s="32"/>
+      <c r="Z40" s="32"/>
+      <c r="AA40" s="32"/>
+      <c r="AB40" s="32"/>
+      <c r="AC40" s="32"/>
+      <c r="AD40" s="32"/>
+      <c r="AE40" s="32"/>
+      <c r="AF40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="32" t="s">
-        <v>529</v>
-      </c>
-      <c r="B41" s="35">
+      <c r="A41" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="B41" s="36">
         <v>1.8</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="36">
         <v>1.36</v>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="36">
         <v>0.84</v>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="36">
         <v>0.97</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="36">
         <v>1.37</v>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="36">
         <v>1.56</v>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="36">
         <v>1.59</v>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="36">
         <v>1.57</v>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="36">
         <v>1.42</v>
       </c>
-      <c r="K41" s="35">
+      <c r="K41" s="36">
         <v>1.69</v>
       </c>
-      <c r="L41" s="35">
+      <c r="L41" s="36">
         <v>1.27</v>
       </c>
-      <c r="M41" s="35">
+      <c r="M41" s="36">
         <v>1.01</v>
       </c>
-      <c r="N41" s="35">
+      <c r="N41" s="36">
         <v>1.82</v>
       </c>
-      <c r="O41" s="35">
+      <c r="O41" s="36">
         <v>2.31</v>
       </c>
-      <c r="P41" s="35">
+      <c r="P41" s="36">
         <v>2.23</v>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="36">
         <v>3.63</v>
       </c>
-      <c r="R41" s="35">
+      <c r="R41" s="36">
         <v>3.07</v>
       </c>
-      <c r="S41" s="35">
+      <c r="S41" s="36">
         <v>0.9</v>
       </c>
-      <c r="T41" s="35">
+      <c r="T41" s="36">
         <v>2.59</v>
       </c>
-      <c r="U41" s="35">
+      <c r="U41" s="36">
         <v>4.94</v>
       </c>
-      <c r="V41" s="35">
+      <c r="V41" s="36">
         <v>5.91</v>
       </c>
-      <c r="W41" s="33"/>
-      <c r="X41" s="35">
+      <c r="W41" s="34"/>
+      <c r="X41" s="36">
         <v>3.53</v>
       </c>
-      <c r="Y41" s="35">
+      <c r="Y41" s="36">
         <v>1.2</v>
       </c>
-      <c r="Z41" s="35">
+      <c r="Z41" s="36">
         <v>0.94</v>
       </c>
-      <c r="AA41" s="35">
+      <c r="AA41" s="36">
         <v>0.97</v>
       </c>
-      <c r="AB41" s="35">
+      <c r="AB41" s="36">
         <v>0.92</v>
       </c>
-      <c r="AC41" s="35">
+      <c r="AC41" s="36">
         <v>0.05</v>
       </c>
-      <c r="AD41" s="35">
+      <c r="AD41" s="36">
         <v>1.16</v>
       </c>
-      <c r="AE41" s="35">
+      <c r="AE41" s="36">
         <v>2.23</v>
       </c>
-      <c r="AF41" s="35">
+      <c r="AF41" s="36">
         <v>1.79</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="32" t="s">
-        <v>530</v>
-      </c>
-      <c r="B42" s="35">
+      <c r="A42" s="33" t="s">
+        <v>531</v>
+      </c>
+      <c r="B42" s="36">
         <v>1.24</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="36">
         <v>1.24</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="36">
         <v>1.31</v>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="36">
         <v>1.44</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="36">
         <v>1.5</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="36">
         <v>1.57</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="36">
         <v>1.51</v>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="36">
         <v>1.39</v>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="36">
         <v>1.47</v>
       </c>
-      <c r="K42" s="35">
+      <c r="K42" s="36">
         <v>1.66</v>
       </c>
-      <c r="L42" s="35">
+      <c r="L42" s="36">
         <v>1.76</v>
       </c>
-      <c r="M42" s="35">
+      <c r="M42" s="36">
         <v>2.17</v>
       </c>
-      <c r="N42" s="35">
+      <c r="N42" s="36">
         <v>2.53</v>
       </c>
-      <c r="O42" s="35">
+      <c r="O42" s="36">
         <v>2.41</v>
       </c>
-      <c r="P42" s="35">
+      <c r="P42" s="36">
         <v>2.48</v>
       </c>
-      <c r="Q42" s="35">
+      <c r="Q42" s="36">
         <v>2.95</v>
       </c>
-      <c r="R42" s="35">
+      <c r="R42" s="36">
         <v>3.19</v>
       </c>
-      <c r="S42" s="35">
+      <c r="S42" s="36">
         <v>3.99</v>
       </c>
-      <c r="T42" s="35">
+      <c r="T42" s="36">
         <v>5.06</v>
       </c>
-      <c r="U42" s="35">
+      <c r="U42" s="36">
         <v>5.12</v>
       </c>
-      <c r="V42" s="35">
+      <c r="V42" s="36">
         <v>3.82</v>
       </c>
-      <c r="W42" s="35">
+      <c r="W42" s="36">
         <v>2.37</v>
       </c>
-      <c r="X42" s="35">
+      <c r="X42" s="36">
         <v>1.32</v>
       </c>
-      <c r="Y42" s="35">
+      <c r="Y42" s="36">
         <v>0.29</v>
       </c>
-      <c r="Z42" s="35">
+      <c r="Z42" s="36">
         <v>0.27</v>
       </c>
-      <c r="AA42" s="35">
+      <c r="AA42" s="36">
         <v>0.26</v>
       </c>
-      <c r="AB42" s="35">
+      <c r="AB42" s="36">
         <v>0.23</v>
       </c>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="33"/>
-      <c r="AE42" s="33"/>
-      <c r="AF42" s="33"/>
+      <c r="AC42" s="34"/>
+      <c r="AD42" s="34"/>
+      <c r="AE42" s="34"/>
+      <c r="AF42" s="34"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="30" t="s">
-        <v>531</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="31"/>
-      <c r="V43" s="31"/>
-      <c r="W43" s="31"/>
-      <c r="X43" s="31"/>
-      <c r="Y43" s="31"/>
-      <c r="Z43" s="31"/>
-      <c r="AA43" s="31"/>
-      <c r="AB43" s="31"/>
-      <c r="AC43" s="31"/>
-      <c r="AD43" s="31"/>
-      <c r="AE43" s="31"/>
-      <c r="AF43" s="31"/>
+      <c r="A43" s="31" t="s">
+        <v>532</v>
+      </c>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
+      <c r="W43" s="32"/>
+      <c r="X43" s="32"/>
+      <c r="Y43" s="32"/>
+      <c r="Z43" s="32"/>
+      <c r="AA43" s="32"/>
+      <c r="AB43" s="32"/>
+      <c r="AC43" s="32"/>
+      <c r="AD43" s="32"/>
+      <c r="AE43" s="32"/>
+      <c r="AF43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="32" t="s">
-        <v>532</v>
-      </c>
-      <c r="B44" s="35">
+      <c r="A44" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="B44" s="36">
         <v>0.41</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <v>0.31</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="36">
         <v>0.19</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="36">
         <v>0.21</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="36">
         <v>0.34</v>
       </c>
-      <c r="G44" s="35">
+      <c r="G44" s="36">
         <v>0.34</v>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="36">
         <v>0.37</v>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="36">
         <v>0.33</v>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="36">
         <v>0.39</v>
       </c>
-      <c r="K44" s="35">
+      <c r="K44" s="36">
         <v>0.55</v>
       </c>
-      <c r="L44" s="35">
+      <c r="L44" s="36">
         <v>0.37</v>
       </c>
-      <c r="M44" s="35">
+      <c r="M44" s="36">
         <v>0.29</v>
       </c>
-      <c r="N44" s="35">
+      <c r="N44" s="36">
         <v>0.71</v>
       </c>
-      <c r="O44" s="35">
+      <c r="O44" s="36">
         <v>0.69</v>
       </c>
-      <c r="P44" s="35">
+      <c r="P44" s="36">
         <v>0.26</v>
       </c>
-      <c r="Q44" s="35">
+      <c r="Q44" s="36">
         <v>0.46</v>
       </c>
-      <c r="R44" s="35">
+      <c r="R44" s="36">
         <v>0.39</v>
       </c>
-      <c r="S44" s="35">
+      <c r="S44" s="36">
         <v>0.11</v>
       </c>
-      <c r="T44" s="35">
+      <c r="T44" s="36">
         <v>0.38</v>
       </c>
-      <c r="U44" s="35">
+      <c r="U44" s="36">
         <v>0.6</v>
       </c>
-      <c r="V44" s="35">
+      <c r="V44" s="36">
         <v>0.57</v>
       </c>
-      <c r="W44" s="35">
+      <c r="W44" s="36">
         <v>0.3</v>
       </c>
-      <c r="X44" s="35">
+      <c r="X44" s="36">
         <v>0.25</v>
       </c>
-      <c r="Y44" s="35">
+      <c r="Y44" s="36">
         <v>0.21</v>
       </c>
-      <c r="Z44" s="35">
+      <c r="Z44" s="36">
         <v>0.18</v>
       </c>
-      <c r="AA44" s="35">
+      <c r="AA44" s="36">
         <v>0.24</v>
       </c>
-      <c r="AB44" s="35">
+      <c r="AB44" s="36">
         <v>0.19</v>
       </c>
-      <c r="AC44" s="35">
+      <c r="AC44" s="36">
         <v>0.14</v>
       </c>
-      <c r="AD44" s="35">
+      <c r="AD44" s="36">
         <v>0.24</v>
       </c>
-      <c r="AE44" s="35">
+      <c r="AE44" s="36">
         <v>0.19</v>
       </c>
-      <c r="AF44" s="35">
+      <c r="AF44" s="36">
         <v>0.14</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="32" t="s">
-        <v>533</v>
-      </c>
-      <c r="B45" s="35">
+      <c r="A45" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="B45" s="36">
         <v>0.29</v>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="36">
         <v>0.28</v>
       </c>
-      <c r="D45" s="35">
+      <c r="D45" s="36">
         <v>0.3</v>
       </c>
-      <c r="E45" s="35">
+      <c r="E45" s="36">
         <v>0.32</v>
       </c>
-      <c r="F45" s="35">
+      <c r="F45" s="36">
         <v>0.35</v>
       </c>
-      <c r="G45" s="35">
+      <c r="G45" s="36">
         <v>0.39</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="36">
         <v>0.4</v>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="36">
         <v>0.38</v>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="36">
         <v>0.46</v>
       </c>
-      <c r="K45" s="35">
+      <c r="K45" s="36">
         <v>0.53</v>
       </c>
-      <c r="L45" s="35">
+      <c r="L45" s="36">
         <v>0.42</v>
       </c>
-      <c r="M45" s="35">
+      <c r="M45" s="36">
         <v>0.44</v>
       </c>
-      <c r="N45" s="35">
+      <c r="N45" s="36">
         <v>0.44</v>
       </c>
-      <c r="O45" s="35">
+      <c r="O45" s="36">
         <v>0.35</v>
       </c>
-      <c r="P45" s="35">
+      <c r="P45" s="36">
         <v>0.32</v>
       </c>
-      <c r="Q45" s="35">
+      <c r="Q45" s="36">
         <v>0.38</v>
       </c>
-      <c r="R45" s="35">
+      <c r="R45" s="36">
         <v>0.4</v>
       </c>
-      <c r="S45" s="35">
+      <c r="S45" s="36">
         <v>0.38</v>
       </c>
-      <c r="T45" s="35">
+      <c r="T45" s="36">
         <v>0.43</v>
       </c>
-      <c r="U45" s="35">
+      <c r="U45" s="36">
         <v>0.41</v>
       </c>
-      <c r="V45" s="35">
+      <c r="V45" s="36">
         <v>0.32</v>
       </c>
-      <c r="W45" s="35">
+      <c r="W45" s="36">
         <v>0.24</v>
       </c>
-      <c r="X45" s="35">
+      <c r="X45" s="36">
         <v>0.21</v>
       </c>
-      <c r="Y45" s="35">
+      <c r="Y45" s="36">
         <v>0.19</v>
       </c>
-      <c r="Z45" s="35">
+      <c r="Z45" s="36">
         <v>0.19</v>
       </c>
-      <c r="AA45" s="35">
+      <c r="AA45" s="36">
         <v>0.2</v>
       </c>
-      <c r="AB45" s="35">
+      <c r="AB45" s="36">
         <v>0.18</v>
       </c>
-      <c r="AC45" s="33"/>
-      <c r="AD45" s="33"/>
-      <c r="AE45" s="33"/>
-      <c r="AF45" s="33"/>
+      <c r="AC45" s="34"/>
+      <c r="AD45" s="34"/>
+      <c r="AE45" s="34"/>
+      <c r="AF45" s="34"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>534</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="31"/>
-      <c r="X46" s="31"/>
-      <c r="Y46" s="31"/>
-      <c r="Z46" s="31"/>
-      <c r="AA46" s="31"/>
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="31"/>
-      <c r="AD46" s="31"/>
-      <c r="AE46" s="31"/>
-      <c r="AF46" s="31"/>
+      <c r="A46" s="31" t="s">
+        <v>535</v>
+      </c>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32"/>
+      <c r="AA46" s="32"/>
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
+      <c r="AD46" s="32"/>
+      <c r="AE46" s="32"/>
+      <c r="AF46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="32" t="s">
-        <v>535</v>
-      </c>
-      <c r="B47" s="35">
+      <c r="A47" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="B47" s="36">
         <v>72.0</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="36">
         <v>10.64</v>
       </c>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="35">
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="36">
         <v>3.4</v>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="36">
         <v>25.14</v>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="36">
         <v>25.0</v>
       </c>
-      <c r="I47" s="35">
+      <c r="I47" s="36">
         <v>7.3</v>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="36">
         <v>3.56</v>
       </c>
-      <c r="K47" s="35">
+      <c r="K47" s="36">
         <v>54.06</v>
       </c>
-      <c r="L47" s="35">
+      <c r="L47" s="36">
         <v>3.47</v>
       </c>
-      <c r="M47" s="35">
+      <c r="M47" s="36">
         <v>3.5</v>
       </c>
-      <c r="N47" s="33"/>
-      <c r="O47" s="35">
+      <c r="N47" s="34"/>
+      <c r="O47" s="36">
         <v>32.03</v>
       </c>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="35">
+      <c r="P47" s="34"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="36">
         <v>5.79</v>
       </c>
-      <c r="S47" s="35">
+      <c r="S47" s="36">
         <v>42.65</v>
       </c>
-      <c r="T47" s="35">
+      <c r="T47" s="36">
         <v>28.97</v>
       </c>
-      <c r="U47" s="33"/>
-      <c r="V47" s="35">
+      <c r="U47" s="34"/>
+      <c r="V47" s="36">
         <v>12.12</v>
       </c>
-      <c r="W47" s="35">
+      <c r="W47" s="36">
         <v>24.35</v>
       </c>
-      <c r="X47" s="33"/>
-      <c r="Y47" s="35">
+      <c r="X47" s="34"/>
+      <c r="Y47" s="36">
         <v>22.17</v>
       </c>
-      <c r="Z47" s="33"/>
-      <c r="AA47" s="35">
+      <c r="Z47" s="34"/>
+      <c r="AA47" s="36">
         <v>19.56</v>
       </c>
-      <c r="AB47" s="35">
+      <c r="AB47" s="36">
         <v>7.65</v>
       </c>
-      <c r="AC47" s="35">
+      <c r="AC47" s="36">
         <v>9.46</v>
       </c>
-      <c r="AD47" s="33"/>
-      <c r="AE47" s="35">
+      <c r="AD47" s="34"/>
+      <c r="AE47" s="36">
         <v>5.75</v>
       </c>
-      <c r="AF47" s="33"/>
+      <c r="AF47" s="34"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>536</v>
-      </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="35">
+      <c r="A48" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="36">
         <v>22.16</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="36">
         <v>6.41</v>
       </c>
-      <c r="G48" s="35">
+      <c r="G48" s="36">
         <v>9.84</v>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="36">
         <v>6.96</v>
       </c>
-      <c r="I48" s="35">
+      <c r="I48" s="36">
         <v>5.34</v>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="36">
         <v>8.93</v>
       </c>
-      <c r="K48" s="35">
+      <c r="K48" s="36">
         <v>16.57</v>
       </c>
-      <c r="L48" s="35">
+      <c r="L48" s="36">
         <v>20.18</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="35">
         <v>151.16</v>
       </c>
-      <c r="N48" s="35">
+      <c r="N48" s="36">
         <v>54.57</v>
       </c>
-      <c r="O48" s="35">
+      <c r="O48" s="36">
         <v>24.89</v>
       </c>
-      <c r="P48" s="35">
+      <c r="P48" s="36">
         <v>24.45</v>
       </c>
-      <c r="Q48" s="35">
+      <c r="Q48" s="36">
         <v>79.11</v>
       </c>
-      <c r="R48" s="35">
+      <c r="R48" s="36">
         <v>27.55</v>
       </c>
-      <c r="S48" s="34">
+      <c r="S48" s="35">
         <v>127.78</v>
       </c>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="34">
+      <c r="T48" s="34"/>
+      <c r="U48" s="34"/>
+      <c r="V48" s="35">
         <v>168.08</v>
       </c>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
-      <c r="Y48" s="35">
+      <c r="W48" s="34"/>
+      <c r="X48" s="34"/>
+      <c r="Y48" s="36">
         <v>25.45</v>
       </c>
-      <c r="Z48" s="35">
+      <c r="Z48" s="36">
         <v>46.86</v>
       </c>
-      <c r="AA48" s="35">
+      <c r="AA48" s="36">
         <v>12.89</v>
       </c>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
+      <c r="AB48" s="34"/>
+      <c r="AC48" s="34"/>
+      <c r="AD48" s="34"/>
+      <c r="AE48" s="34"/>
+      <c r="AF48" s="34"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>537</v>
-      </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="31"/>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="31"/>
-      <c r="S49" s="31"/>
-      <c r="T49" s="31"/>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31"/>
-      <c r="X49" s="31"/>
-      <c r="Y49" s="31"/>
-      <c r="Z49" s="31"/>
-      <c r="AA49" s="31"/>
-      <c r="AB49" s="31"/>
-      <c r="AC49" s="31"/>
-      <c r="AD49" s="31"/>
-      <c r="AE49" s="31"/>
-      <c r="AF49" s="31"/>
+      <c r="A49" s="31" t="s">
+        <v>538</v>
+      </c>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="32"/>
+      <c r="X49" s="32"/>
+      <c r="Y49" s="32"/>
+      <c r="Z49" s="32"/>
+      <c r="AA49" s="32"/>
+      <c r="AB49" s="32"/>
+      <c r="AC49" s="32"/>
+      <c r="AD49" s="32"/>
+      <c r="AE49" s="32"/>
+      <c r="AF49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="32" t="s">
-        <v>538</v>
-      </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="35">
+      <c r="A50" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="36">
         <v>13.0</v>
       </c>
-      <c r="E50" s="35">
+      <c r="E50" s="36">
         <v>5.37</v>
       </c>
-      <c r="F50" s="35">
+      <c r="F50" s="36">
         <v>22.6</v>
       </c>
-      <c r="G50" s="35">
+      <c r="G50" s="36">
         <v>30.31</v>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="36">
         <v>20.83</v>
       </c>
-      <c r="I50" s="35">
+      <c r="I50" s="36">
         <v>13.49</v>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="36">
         <v>10.89</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>131.3</v>
       </c>
-      <c r="L50" s="35">
+      <c r="L50" s="36">
         <v>10.77</v>
       </c>
-      <c r="M50" s="35">
+      <c r="M50" s="36">
         <v>7.56</v>
       </c>
-      <c r="N50" s="35">
+      <c r="N50" s="36">
         <v>12.56</v>
       </c>
-      <c r="O50" s="35">
+      <c r="O50" s="36">
         <v>7.41</v>
       </c>
-      <c r="P50" s="35">
+      <c r="P50" s="36">
         <v>7.01</v>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="36">
         <v>13.22</v>
       </c>
-      <c r="R50" s="35">
+      <c r="R50" s="36">
         <v>22.01</v>
       </c>
-      <c r="S50" s="35">
+      <c r="S50" s="36">
         <v>4.11</v>
       </c>
-      <c r="T50" s="35">
+      <c r="T50" s="36">
         <v>7.47</v>
       </c>
-      <c r="U50" s="35">
+      <c r="U50" s="36">
         <v>13.0</v>
       </c>
-      <c r="V50" s="35">
+      <c r="V50" s="36">
         <v>8.78</v>
       </c>
-      <c r="W50" s="35">
+      <c r="W50" s="36">
         <v>9.34</v>
       </c>
-      <c r="X50" s="35">
+      <c r="X50" s="36">
         <v>11.49</v>
       </c>
-      <c r="Y50" s="35">
+      <c r="Y50" s="36">
         <v>7.52</v>
       </c>
-      <c r="Z50" s="35">
+      <c r="Z50" s="36">
         <v>4.7</v>
       </c>
-      <c r="AA50" s="35">
+      <c r="AA50" s="36">
         <v>5.89</v>
       </c>
-      <c r="AB50" s="35">
+      <c r="AB50" s="36">
         <v>3.28</v>
       </c>
-      <c r="AC50" s="35">
+      <c r="AC50" s="36">
         <v>4.9</v>
       </c>
-      <c r="AD50" s="35">
+      <c r="AD50" s="36">
         <v>4.9</v>
       </c>
-      <c r="AE50" s="35">
+      <c r="AE50" s="36">
         <v>4.59</v>
       </c>
-      <c r="AF50" s="35">
+      <c r="AF50" s="36">
         <v>8.93</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="32" t="s">
-        <v>539</v>
-      </c>
-      <c r="B51" s="35">
+      <c r="A51" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="B51" s="36">
         <v>33.99</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="36">
         <v>26.46</v>
       </c>
-      <c r="D51" s="35">
+      <c r="D51" s="36">
         <v>15.71</v>
       </c>
-      <c r="E51" s="35">
+      <c r="E51" s="36">
         <v>15.42</v>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="36">
         <v>16.72</v>
       </c>
-      <c r="G51" s="35">
+      <c r="G51" s="36">
         <v>20.36</v>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="36">
         <v>16.87</v>
       </c>
-      <c r="I51" s="35">
+      <c r="I51" s="36">
         <v>13.79</v>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="36">
         <v>13.44</v>
       </c>
-      <c r="K51" s="35">
+      <c r="K51" s="36">
         <v>11.18</v>
       </c>
-      <c r="L51" s="35">
+      <c r="L51" s="36">
         <v>8.53</v>
       </c>
-      <c r="M51" s="35">
+      <c r="M51" s="36">
         <v>9.28</v>
       </c>
-      <c r="N51" s="35">
+      <c r="N51" s="36">
         <v>10.68</v>
       </c>
-      <c r="O51" s="35">
+      <c r="O51" s="36">
         <v>9.34</v>
       </c>
-      <c r="P51" s="35">
+      <c r="P51" s="36">
         <v>9.36</v>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="36">
         <v>10.83</v>
       </c>
-      <c r="R51" s="35">
+      <c r="R51" s="36">
         <v>9.81</v>
       </c>
-      <c r="S51" s="35">
+      <c r="S51" s="36">
         <v>8.72</v>
       </c>
-      <c r="T51" s="35">
+      <c r="T51" s="36">
         <v>9.65</v>
       </c>
-      <c r="U51" s="35">
+      <c r="U51" s="36">
         <v>10.2</v>
       </c>
-      <c r="V51" s="35">
+      <c r="V51" s="36">
         <v>8.48</v>
       </c>
-      <c r="W51" s="35">
+      <c r="W51" s="36">
         <v>7.85</v>
       </c>
-      <c r="X51" s="35">
+      <c r="X51" s="36">
         <v>6.24</v>
       </c>
-      <c r="Y51" s="35">
+      <c r="Y51" s="36">
         <v>5.07</v>
       </c>
-      <c r="Z51" s="35">
+      <c r="Z51" s="36">
         <v>4.59</v>
       </c>
-      <c r="AA51" s="35">
+      <c r="AA51" s="36">
         <v>4.57</v>
       </c>
-      <c r="AB51" s="35">
+      <c r="AB51" s="36">
         <v>4.51</v>
       </c>
-      <c r="AC51" s="33"/>
-      <c r="AD51" s="33"/>
-      <c r="AE51" s="33"/>
-      <c r="AF51" s="33"/>
+      <c r="AC51" s="34"/>
+      <c r="AD51" s="34"/>
+      <c r="AE51" s="34"/>
+      <c r="AF51" s="34"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>540</v>
-      </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
-      <c r="N52" s="31"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="31"/>
-      <c r="S52" s="31"/>
-      <c r="T52" s="31"/>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
-      <c r="W52" s="31"/>
-      <c r="X52" s="31"/>
-      <c r="Y52" s="31"/>
-      <c r="Z52" s="31"/>
-      <c r="AA52" s="31"/>
-      <c r="AB52" s="31"/>
-      <c r="AC52" s="31"/>
-      <c r="AD52" s="31"/>
-      <c r="AE52" s="31"/>
-      <c r="AF52" s="31"/>
+      <c r="A52" s="31" t="s">
+        <v>541</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="32"/>
+      <c r="Y52" s="32"/>
+      <c r="Z52" s="32"/>
+      <c r="AA52" s="32"/>
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32"/>
+      <c r="AF52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="32" t="s">
-        <v>541</v>
-      </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="34">
+      <c r="A53" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="35">
         <v>138.71</v>
       </c>
-      <c r="E53" s="35">
+      <c r="E53" s="36">
         <v>8.18</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <v>180.8</v>
       </c>
-      <c r="G53" s="33"/>
-      <c r="H53" s="34">
+      <c r="G53" s="34"/>
+      <c r="H53" s="35">
         <v>280.08</v>
       </c>
-      <c r="I53" s="35">
+      <c r="I53" s="36">
         <v>26.54</v>
       </c>
-      <c r="J53" s="35">
+      <c r="J53" s="36">
         <v>13.64</v>
       </c>
-      <c r="K53" s="33"/>
-      <c r="L53" s="35">
+      <c r="K53" s="34"/>
+      <c r="L53" s="36">
         <v>13.56</v>
       </c>
-      <c r="M53" s="35">
+      <c r="M53" s="36">
         <v>9.25</v>
       </c>
-      <c r="N53" s="35">
+      <c r="N53" s="36">
         <v>17.49</v>
       </c>
-      <c r="O53" s="35">
+      <c r="O53" s="36">
         <v>9.85</v>
       </c>
-      <c r="P53" s="35">
+      <c r="P53" s="36">
         <v>9.28</v>
       </c>
-      <c r="Q53" s="35">
+      <c r="Q53" s="36">
         <v>12.38</v>
       </c>
-      <c r="R53" s="35">
+      <c r="R53" s="36">
         <v>19.71</v>
       </c>
-      <c r="S53" s="35">
+      <c r="S53" s="36">
         <v>3.26</v>
       </c>
-      <c r="T53" s="35">
+      <c r="T53" s="36">
         <v>6.31</v>
       </c>
-      <c r="U53" s="35">
+      <c r="U53" s="36">
         <v>11.57</v>
       </c>
-      <c r="V53" s="35">
+      <c r="V53" s="36">
         <v>11.16</v>
       </c>
-      <c r="W53" s="35">
+      <c r="W53" s="36">
         <v>8.53</v>
       </c>
-      <c r="X53" s="35">
+      <c r="X53" s="36">
         <v>12.27</v>
       </c>
-      <c r="Y53" s="35">
+      <c r="Y53" s="36">
         <v>8.45</v>
       </c>
-      <c r="Z53" s="35">
+      <c r="Z53" s="36">
         <v>4.7</v>
       </c>
-      <c r="AA53" s="35">
+      <c r="AA53" s="36">
         <v>5.33</v>
       </c>
-      <c r="AB53" s="35">
+      <c r="AB53" s="36">
         <v>3.86</v>
       </c>
-      <c r="AC53" s="35">
+      <c r="AC53" s="36">
         <v>5.68</v>
       </c>
-      <c r="AD53" s="35">
+      <c r="AD53" s="36">
         <v>5.51</v>
       </c>
-      <c r="AE53" s="35">
+      <c r="AE53" s="36">
         <v>7.75</v>
       </c>
-      <c r="AF53" s="34">
+      <c r="AF53" s="35">
         <v>882.59</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="32" t="s">
-        <v>542</v>
-      </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="35">
+      <c r="A54" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="36">
         <v>61.02</v>
       </c>
-      <c r="E54" s="35">
+      <c r="E54" s="36">
         <v>45.53</v>
       </c>
-      <c r="F54" s="35">
+      <c r="F54" s="36">
         <v>40.73</v>
       </c>
-      <c r="G54" s="35">
+      <c r="G54" s="36">
         <v>51.76</v>
       </c>
-      <c r="H54" s="35">
+      <c r="H54" s="36">
         <v>30.19</v>
       </c>
-      <c r="I54" s="35">
+      <c r="I54" s="36">
         <v>19.76</v>
       </c>
-      <c r="J54" s="35">
+      <c r="J54" s="36">
         <v>18.3</v>
       </c>
-      <c r="K54" s="35">
+      <c r="K54" s="36">
         <v>15.29</v>
       </c>
-      <c r="L54" s="35">
+      <c r="L54" s="36">
         <v>11.23</v>
       </c>
-      <c r="M54" s="35">
+      <c r="M54" s="36">
         <v>11.33</v>
       </c>
-      <c r="N54" s="35">
+      <c r="N54" s="36">
         <v>12.6</v>
       </c>
-      <c r="O54" s="35">
+      <c r="O54" s="36">
         <v>10.01</v>
       </c>
-      <c r="P54" s="35">
+      <c r="P54" s="36">
         <v>8.84</v>
       </c>
-      <c r="Q54" s="35">
+      <c r="Q54" s="36">
         <v>9.4</v>
       </c>
-      <c r="R54" s="35">
+      <c r="R54" s="36">
         <v>9.19</v>
       </c>
-      <c r="S54" s="35">
+      <c r="S54" s="36">
         <v>8.18</v>
       </c>
-      <c r="T54" s="35">
+      <c r="T54" s="36">
         <v>9.41</v>
       </c>
-      <c r="U54" s="35">
+      <c r="U54" s="36">
         <v>10.65</v>
       </c>
-      <c r="V54" s="35">
+      <c r="V54" s="36">
         <v>9.32</v>
       </c>
-      <c r="W54" s="35">
+      <c r="W54" s="36">
         <v>7.73</v>
       </c>
-      <c r="X54" s="35">
+      <c r="X54" s="36">
         <v>6.57</v>
       </c>
-      <c r="Y54" s="35">
+      <c r="Y54" s="36">
         <v>5.39</v>
       </c>
-      <c r="Z54" s="35">
+      <c r="Z54" s="36">
         <v>4.88</v>
       </c>
-      <c r="AA54" s="35">
+      <c r="AA54" s="36">
         <v>5.28</v>
       </c>
-      <c r="AB54" s="35">
+      <c r="AB54" s="36">
         <v>5.98</v>
       </c>
-      <c r="AC54" s="33"/>
-      <c r="AD54" s="33"/>
-      <c r="AE54" s="33"/>
-      <c r="AF54" s="33"/>
+      <c r="AC54" s="34"/>
+      <c r="AD54" s="34"/>
+      <c r="AE54" s="34"/>
+      <c r="AF54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>543</v>
-      </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
-      <c r="Q55" s="31"/>
-      <c r="R55" s="31"/>
-      <c r="S55" s="31"/>
-      <c r="T55" s="31"/>
-      <c r="U55" s="31"/>
-      <c r="V55" s="31"/>
-      <c r="W55" s="31"/>
-      <c r="X55" s="31"/>
-      <c r="Y55" s="31"/>
-      <c r="Z55" s="31"/>
-      <c r="AA55" s="31"/>
-      <c r="AB55" s="31"/>
-      <c r="AC55" s="31"/>
-      <c r="AD55" s="31"/>
-      <c r="AE55" s="31"/>
-      <c r="AF55" s="31"/>
+      <c r="A55" s="31" t="s">
+        <v>544</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
+      <c r="Z55" s="32"/>
+      <c r="AA55" s="32"/>
+      <c r="AB55" s="32"/>
+      <c r="AC55" s="32"/>
+      <c r="AD55" s="32"/>
+      <c r="AE55" s="32"/>
+      <c r="AF55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="35">
+      <c r="A56" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="36">
         <v>8.44</v>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="35">
         <v>225.98</v>
       </c>
-      <c r="G56" s="35">
+      <c r="G56" s="36">
         <v>57.26</v>
       </c>
-      <c r="H56" s="33"/>
-      <c r="I56" s="35">
+      <c r="H56" s="34"/>
+      <c r="I56" s="36">
         <v>15.01</v>
       </c>
-      <c r="J56" s="35">
+      <c r="J56" s="36">
         <v>13.64</v>
       </c>
-      <c r="K56" s="33"/>
-      <c r="L56" s="35">
+      <c r="K56" s="34"/>
+      <c r="L56" s="36">
         <v>10.87</v>
       </c>
-      <c r="M56" s="35">
+      <c r="M56" s="36">
         <v>8.5</v>
       </c>
-      <c r="N56" s="35">
+      <c r="N56" s="36">
         <v>22.03</v>
       </c>
-      <c r="O56" s="35">
+      <c r="O56" s="36">
         <v>9.62</v>
       </c>
-      <c r="P56" s="35">
+      <c r="P56" s="36">
         <v>3.63</v>
       </c>
-      <c r="Q56" s="35">
+      <c r="Q56" s="36">
         <v>5.19</v>
       </c>
-      <c r="R56" s="33"/>
-      <c r="S56" s="33"/>
-      <c r="T56" s="35">
+      <c r="R56" s="34"/>
+      <c r="S56" s="34"/>
+      <c r="T56" s="36">
         <v>3.27</v>
       </c>
-      <c r="U56" s="35">
+      <c r="U56" s="36">
         <v>5.58</v>
       </c>
-      <c r="V56" s="35">
+      <c r="V56" s="36">
         <v>11.16</v>
       </c>
-      <c r="W56" s="33"/>
-      <c r="X56" s="35">
+      <c r="W56" s="34"/>
+      <c r="X56" s="36">
         <v>21.62</v>
       </c>
-      <c r="Y56" s="35">
+      <c r="Y56" s="36">
         <v>11.71</v>
       </c>
-      <c r="Z56" s="35">
+      <c r="Z56" s="36">
         <v>6.52</v>
       </c>
-      <c r="AA56" s="35">
+      <c r="AA56" s="36">
         <v>8.25</v>
       </c>
-      <c r="AB56" s="35">
+      <c r="AB56" s="36">
         <v>4.39</v>
       </c>
-      <c r="AC56" s="35">
+      <c r="AC56" s="36">
         <v>10.05</v>
       </c>
-      <c r="AD56" s="35">
+      <c r="AD56" s="36">
         <v>10.38</v>
       </c>
-      <c r="AE56" s="35">
+      <c r="AE56" s="36">
         <v>7.12</v>
       </c>
-      <c r="AF56" s="35">
+      <c r="AF56" s="36">
         <v>31.23</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="32" t="s">
-        <v>545</v>
-      </c>
-      <c r="B57" s="35">
+      <c r="A57" s="33" t="s">
+        <v>546</v>
+      </c>
+      <c r="B57" s="36">
         <v>0.83</v>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <v>0.85</v>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <v>0.93</v>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <v>1.01</v>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <v>1.13</v>
       </c>
-      <c r="G57" s="35">
+      <c r="G57" s="36">
         <v>1.26</v>
       </c>
-      <c r="H57" s="35">
+      <c r="H57" s="36">
         <v>1.27</v>
       </c>
-      <c r="I57" s="35">
+      <c r="I57" s="36">
         <v>1.24</v>
       </c>
-      <c r="J57" s="35">
+      <c r="J57" s="36">
         <v>1.42</v>
       </c>
-      <c r="K57" s="35">
+      <c r="K57" s="36">
         <v>1.41</v>
       </c>
-      <c r="L57" s="35">
+      <c r="L57" s="36">
         <v>1.34</v>
       </c>
-      <c r="M57" s="35">
+      <c r="M57" s="36">
         <v>1.49</v>
       </c>
-      <c r="N57" s="35">
+      <c r="N57" s="36">
         <v>1.61</v>
       </c>
-      <c r="O57" s="35">
+      <c r="O57" s="36">
         <v>1.39</v>
       </c>
-      <c r="P57" s="35">
+      <c r="P57" s="36">
         <v>1.46</v>
       </c>
-      <c r="Q57" s="35">
+      <c r="Q57" s="36">
         <v>1.76</v>
       </c>
-      <c r="R57" s="35">
+      <c r="R57" s="36">
         <v>1.9</v>
       </c>
-      <c r="S57" s="35">
+      <c r="S57" s="36">
         <v>1.93</v>
       </c>
-      <c r="T57" s="35">
+      <c r="T57" s="36">
         <v>2.25</v>
       </c>
-      <c r="U57" s="35">
+      <c r="U57" s="36">
         <v>2.22</v>
       </c>
-      <c r="V57" s="35">
+      <c r="V57" s="36">
         <v>1.76</v>
       </c>
-      <c r="W57" s="35">
+      <c r="W57" s="36">
         <v>1.27</v>
       </c>
-      <c r="X57" s="35">
+      <c r="X57" s="36">
         <v>1.05</v>
       </c>
-      <c r="Y57" s="35">
+      <c r="Y57" s="36">
         <v>0.28</v>
       </c>
-      <c r="Z57" s="35">
+      <c r="Z57" s="36">
         <v>0.26</v>
       </c>
-      <c r="AA57" s="35">
+      <c r="AA57" s="36">
         <v>0.25</v>
       </c>
-      <c r="AB57" s="35">
+      <c r="AB57" s="36">
         <v>0.22</v>
       </c>
-      <c r="AC57" s="33"/>
-      <c r="AD57" s="33"/>
-      <c r="AE57" s="33"/>
-      <c r="AF57" s="33"/>
+      <c r="AC57" s="34"/>
+      <c r="AD57" s="34"/>
+      <c r="AE57" s="34"/>
+      <c r="AF57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>546</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
-      <c r="X58" s="31"/>
-      <c r="Y58" s="31"/>
-      <c r="Z58" s="31"/>
-      <c r="AA58" s="31"/>
-      <c r="AB58" s="31"/>
-      <c r="AC58" s="31"/>
-      <c r="AD58" s="31"/>
-      <c r="AE58" s="31"/>
-      <c r="AF58" s="31"/>
+      <c r="A58" s="31" t="s">
+        <v>547</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
+      <c r="X58" s="32"/>
+      <c r="Y58" s="32"/>
+      <c r="Z58" s="32"/>
+      <c r="AA58" s="32"/>
+      <c r="AB58" s="32"/>
+      <c r="AC58" s="32"/>
+      <c r="AD58" s="32"/>
+      <c r="AE58" s="32"/>
+      <c r="AF58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="32" t="s">
-        <v>547</v>
-      </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="38">
+      <c r="A59" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="39">
         <v>-1.46</v>
       </c>
-      <c r="E59" s="35">
+      <c r="E59" s="36">
         <v>0.01</v>
       </c>
-      <c r="F59" s="35">
+      <c r="F59" s="36">
         <v>1.11</v>
       </c>
-      <c r="G59" s="33"/>
-      <c r="H59" s="38">
+      <c r="G59" s="34"/>
+      <c r="H59" s="39">
         <v>-3.15</v>
       </c>
-      <c r="I59" s="38">
+      <c r="I59" s="39">
         <v>-0.46</v>
       </c>
-      <c r="J59" s="35">
+      <c r="J59" s="36">
         <v>0.02</v>
       </c>
-      <c r="K59" s="33"/>
-      <c r="L59" s="38">
+      <c r="K59" s="34"/>
+      <c r="L59" s="39">
         <v>-0.83</v>
       </c>
-      <c r="M59" s="38">
+      <c r="M59" s="39">
         <v>-0.45</v>
       </c>
-      <c r="N59" s="38">
+      <c r="N59" s="39">
         <v>-0.35</v>
       </c>
-      <c r="O59" s="35">
+      <c r="O59" s="36">
         <v>0.79</v>
       </c>
-      <c r="P59" s="38">
+      <c r="P59" s="39">
         <v>-0.81</v>
       </c>
-      <c r="Q59" s="35">
+      <c r="Q59" s="36">
         <v>0.12</v>
       </c>
-      <c r="R59" s="38">
+      <c r="R59" s="39">
         <v>-0.41</v>
       </c>
-      <c r="S59" s="38">
+      <c r="S59" s="39">
         <v>-0.08</v>
       </c>
-      <c r="T59" s="35">
+      <c r="T59" s="36">
         <v>0.2</v>
       </c>
-      <c r="U59" s="35">
+      <c r="U59" s="36">
         <v>0.98</v>
       </c>
-      <c r="V59" s="35">
+      <c r="V59" s="36">
         <v>0.22</v>
       </c>
-      <c r="W59" s="35">
+      <c r="W59" s="36">
         <v>0.09</v>
       </c>
-      <c r="X59" s="35">
+      <c r="X59" s="36">
         <v>1.18</v>
       </c>
-      <c r="Y59" s="38">
+      <c r="Y59" s="39">
         <v>-0.27</v>
       </c>
-      <c r="Z59" s="35">
+      <c r="Z59" s="36">
         <v>0.37</v>
       </c>
-      <c r="AA59" s="38">
+      <c r="AA59" s="39">
         <v>-0.56</v>
       </c>
-      <c r="AB59" s="35">
+      <c r="AB59" s="36">
         <v>0.03</v>
       </c>
-      <c r="AC59" s="38">
+      <c r="AC59" s="39">
         <v>-0.19</v>
       </c>
-      <c r="AD59" s="35">
+      <c r="AD59" s="36">
         <v>0.09</v>
       </c>
-      <c r="AE59" s="33">
+      <c r="AE59" s="34">
         <v>0.0</v>
       </c>
-      <c r="AF59" s="33"/>
+      <c r="AF59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="32" t="s">
-        <v>548</v>
-      </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="38">
+      <c r="A60" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="39">
         <v>-1.51</v>
       </c>
-      <c r="E60" s="38">
+      <c r="E60" s="39">
         <v>-5.88</v>
       </c>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="38">
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="39">
         <v>-0.66</v>
       </c>
-      <c r="I60" s="38">
+      <c r="I60" s="39">
         <v>-1.03</v>
       </c>
-      <c r="J60" s="38">
+      <c r="J60" s="39">
         <v>-1.1</v>
       </c>
-      <c r="K60" s="33"/>
-      <c r="L60" s="38">
+      <c r="K60" s="34"/>
+      <c r="L60" s="39">
         <v>-0.57</v>
       </c>
-      <c r="M60" s="38">
+      <c r="M60" s="39">
         <v>-2.83</v>
       </c>
-      <c r="N60" s="38">
+      <c r="N60" s="39">
         <v>-1.07</v>
       </c>
-      <c r="O60" s="38">
+      <c r="O60" s="39">
         <v>-1.14</v>
       </c>
-      <c r="P60" s="38">
+      <c r="P60" s="39">
         <v>-1.49</v>
       </c>
-      <c r="Q60" s="38">
+      <c r="Q60" s="39">
         <v>-6.54</v>
       </c>
-      <c r="R60" s="38">
+      <c r="R60" s="39">
         <v>-1.24</v>
       </c>
-      <c r="S60" s="35">
+      <c r="S60" s="36">
         <v>0.4</v>
       </c>
-      <c r="T60" s="35">
+      <c r="T60" s="36">
         <v>0.26</v>
       </c>
-      <c r="U60" s="35">
+      <c r="U60" s="36">
         <v>0.52</v>
       </c>
-      <c r="V60" s="35">
+      <c r="V60" s="36">
         <v>0.46</v>
       </c>
-      <c r="W60" s="35">
+      <c r="W60" s="36">
         <v>0.88</v>
       </c>
-      <c r="X60" s="35">
+      <c r="X60" s="36">
         <v>0.6</v>
       </c>
-      <c r="Y60" s="35">
+      <c r="Y60" s="36">
         <v>4.67</v>
       </c>
-      <c r="Z60" s="35">
+      <c r="Z60" s="36">
         <v>0.25</v>
       </c>
-      <c r="AA60" s="35">
+      <c r="AA60" s="36">
         <v>0.02</v>
       </c>
-      <c r="AB60" s="33"/>
-      <c r="AC60" s="33"/>
-      <c r="AD60" s="33"/>
-      <c r="AE60" s="33"/>
-      <c r="AF60" s="33"/>
+      <c r="AB60" s="34"/>
+      <c r="AC60" s="34"/>
+      <c r="AD60" s="34"/>
+      <c r="AE60" s="34"/>
+      <c r="AF60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
-        <v>549</v>
-      </c>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="31"/>
-      <c r="Q61" s="31"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
-      <c r="X61" s="31"/>
-      <c r="Y61" s="31"/>
-      <c r="Z61" s="31"/>
-      <c r="AA61" s="31"/>
-      <c r="AB61" s="31"/>
-      <c r="AC61" s="31"/>
-      <c r="AD61" s="31"/>
-      <c r="AE61" s="31"/>
-      <c r="AF61" s="31"/>
+      <c r="A61" s="31" t="s">
+        <v>550</v>
+      </c>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="32"/>
+      <c r="X61" s="32"/>
+      <c r="Y61" s="32"/>
+      <c r="Z61" s="32"/>
+      <c r="AA61" s="32"/>
+      <c r="AB61" s="32"/>
+      <c r="AC61" s="32"/>
+      <c r="AD61" s="32"/>
+      <c r="AE61" s="32"/>
+      <c r="AF61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="32" t="s">
-        <v>550</v>
-      </c>
-      <c r="B62" s="35">
+      <c r="A62" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="B62" s="36">
         <v>0.86</v>
       </c>
-      <c r="C62" s="35">
+      <c r="C62" s="36">
         <v>0.79</v>
       </c>
-      <c r="D62" s="35">
+      <c r="D62" s="36">
         <v>0.64</v>
       </c>
-      <c r="E62" s="35">
+      <c r="E62" s="36">
         <v>0.48</v>
       </c>
-      <c r="F62" s="35">
+      <c r="F62" s="36">
         <v>0.48</v>
       </c>
-      <c r="G62" s="35">
+      <c r="G62" s="36">
         <v>0.57</v>
       </c>
-      <c r="H62" s="35">
+      <c r="H62" s="36">
         <v>0.64</v>
       </c>
-      <c r="I62" s="35">
+      <c r="I62" s="36">
         <v>0.54</v>
       </c>
-      <c r="J62" s="35">
+      <c r="J62" s="36">
         <v>0.64</v>
       </c>
-      <c r="K62" s="35">
+      <c r="K62" s="36">
         <v>0.93</v>
       </c>
-      <c r="L62" s="35">
+      <c r="L62" s="36">
         <v>0.68</v>
       </c>
-      <c r="M62" s="35">
+      <c r="M62" s="36">
         <v>0.69</v>
       </c>
-      <c r="N62" s="35">
+      <c r="N62" s="36">
         <v>1.16</v>
       </c>
-      <c r="O62" s="35">
+      <c r="O62" s="36">
         <v>1.08</v>
       </c>
-      <c r="P62" s="35">
+      <c r="P62" s="36">
         <v>0.36</v>
       </c>
-      <c r="Q62" s="35">
+      <c r="Q62" s="36">
         <v>0.59</v>
       </c>
-      <c r="R62" s="35">
+      <c r="R62" s="36">
         <v>0.52</v>
       </c>
-      <c r="S62" s="35">
+      <c r="S62" s="36">
         <v>0.23</v>
       </c>
-      <c r="T62" s="35">
+      <c r="T62" s="36">
         <v>0.49</v>
       </c>
-      <c r="U62" s="35">
+      <c r="U62" s="36">
         <v>0.7</v>
       </c>
-      <c r="V62" s="35">
+      <c r="V62" s="36">
         <v>0.6</v>
       </c>
-      <c r="W62" s="35">
+      <c r="W62" s="36">
         <v>0.38</v>
       </c>
-      <c r="X62" s="35">
+      <c r="X62" s="36">
         <v>0.43</v>
       </c>
-      <c r="Y62" s="35">
+      <c r="Y62" s="36">
         <v>0.36</v>
       </c>
-      <c r="Z62" s="35">
+      <c r="Z62" s="36">
         <v>0.32</v>
       </c>
-      <c r="AA62" s="35">
+      <c r="AA62" s="36">
         <v>0.43</v>
       </c>
-      <c r="AB62" s="35">
+      <c r="AB62" s="36">
         <v>0.36</v>
       </c>
-      <c r="AC62" s="35">
+      <c r="AC62" s="36">
         <v>0.32</v>
       </c>
-      <c r="AD62" s="35">
+      <c r="AD62" s="36">
         <v>0.45</v>
       </c>
-      <c r="AE62" s="35">
+      <c r="AE62" s="36">
         <v>0.47</v>
       </c>
-      <c r="AF62" s="35">
+      <c r="AF62" s="36">
         <v>0.54</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="32" t="s">
-        <v>551</v>
-      </c>
-      <c r="B63" s="35">
+      <c r="A63" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="B63" s="36">
         <v>0.63</v>
       </c>
-      <c r="C63" s="35">
+      <c r="C63" s="36">
         <v>0.58</v>
       </c>
-      <c r="D63" s="35">
+      <c r="D63" s="36">
         <v>0.56</v>
       </c>
-      <c r="E63" s="35">
+      <c r="E63" s="36">
         <v>0.55</v>
       </c>
-      <c r="F63" s="35">
+      <c r="F63" s="36">
         <v>0.57</v>
       </c>
-      <c r="G63" s="35">
+      <c r="G63" s="36">
         <v>0.64</v>
       </c>
-      <c r="H63" s="35">
+      <c r="H63" s="36">
         <v>0.66</v>
       </c>
-      <c r="I63" s="35">
+      <c r="I63" s="36">
         <v>0.67</v>
       </c>
-      <c r="J63" s="35">
+      <c r="J63" s="36">
         <v>0.81</v>
       </c>
-      <c r="K63" s="35">
+      <c r="K63" s="36">
         <v>0.91</v>
       </c>
-      <c r="L63" s="35">
+      <c r="L63" s="36">
         <v>0.7</v>
       </c>
-      <c r="M63" s="35">
+      <c r="M63" s="36">
         <v>0.67</v>
       </c>
-      <c r="N63" s="35">
+      <c r="N63" s="36">
         <v>0.64</v>
       </c>
-      <c r="O63" s="35">
+      <c r="O63" s="36">
         <v>0.49</v>
       </c>
-      <c r="P63" s="35">
+      <c r="P63" s="36">
         <v>0.43</v>
       </c>
-      <c r="Q63" s="35">
+      <c r="Q63" s="36">
         <v>0.5</v>
       </c>
-      <c r="R63" s="35">
+      <c r="R63" s="36">
         <v>0.49</v>
       </c>
-      <c r="S63" s="35">
+      <c r="S63" s="36">
         <v>0.47</v>
       </c>
-      <c r="T63" s="35">
+      <c r="T63" s="36">
         <v>0.53</v>
       </c>
-      <c r="U63" s="35">
+      <c r="U63" s="36">
         <v>0.52</v>
       </c>
-      <c r="V63" s="35">
+      <c r="V63" s="36">
         <v>0.44</v>
       </c>
-      <c r="W63" s="35">
+      <c r="W63" s="36">
         <v>0.39</v>
       </c>
-      <c r="X63" s="35">
+      <c r="X63" s="36">
         <v>0.38</v>
       </c>
-      <c r="Y63" s="35">
+      <c r="Y63" s="36">
         <v>0.36</v>
       </c>
-      <c r="Z63" s="35">
+      <c r="Z63" s="36">
         <v>0.37</v>
       </c>
-      <c r="AA63" s="35">
+      <c r="AA63" s="36">
         <v>0.4</v>
       </c>
-      <c r="AB63" s="35">
+      <c r="AB63" s="36">
         <v>0.41</v>
       </c>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
-      <c r="AE63" s="33"/>
-      <c r="AF63" s="33"/>
+      <c r="AC63" s="34"/>
+      <c r="AD63" s="34"/>
+      <c r="AE63" s="34"/>
+      <c r="AF63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
-      <c r="X64" s="31"/>
-      <c r="Y64" s="31"/>
-      <c r="Z64" s="31"/>
-      <c r="AA64" s="31"/>
-      <c r="AB64" s="31"/>
-      <c r="AC64" s="31"/>
-      <c r="AD64" s="31"/>
-      <c r="AE64" s="31"/>
-      <c r="AF64" s="31"/>
+      <c r="A64" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
+      <c r="X64" s="32"/>
+      <c r="Y64" s="32"/>
+      <c r="Z64" s="32"/>
+      <c r="AA64" s="32"/>
+      <c r="AB64" s="32"/>
+      <c r="AC64" s="32"/>
+      <c r="AD64" s="32"/>
+      <c r="AE64" s="32"/>
+      <c r="AF64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="32" t="s">
-        <v>553</v>
-      </c>
-      <c r="B65" s="35">
+      <c r="A65" s="33" t="s">
+        <v>554</v>
+      </c>
+      <c r="B65" s="36">
         <v>24.07</v>
       </c>
-      <c r="C65" s="35">
+      <c r="C65" s="36">
         <v>21.07</v>
       </c>
-      <c r="D65" s="35">
+      <c r="D65" s="36">
         <v>26.19</v>
       </c>
-      <c r="E65" s="35">
+      <c r="E65" s="36">
         <v>10.32</v>
       </c>
-      <c r="F65" s="35">
+      <c r="F65" s="36">
         <v>19.04</v>
       </c>
-      <c r="G65" s="35">
+      <c r="G65" s="36">
         <v>24.14</v>
       </c>
-      <c r="H65" s="35">
+      <c r="H65" s="36">
         <v>42.43</v>
       </c>
-      <c r="I65" s="35">
+      <c r="I65" s="36">
         <v>11.94</v>
       </c>
-      <c r="J65" s="35">
+      <c r="J65" s="36">
         <v>19.34</v>
       </c>
-      <c r="K65" s="35">
+      <c r="K65" s="36">
         <v>67.71</v>
       </c>
-      <c r="L65" s="35">
+      <c r="L65" s="36">
         <v>12.42</v>
       </c>
-      <c r="M65" s="35">
+      <c r="M65" s="36">
         <v>12.39</v>
       </c>
-      <c r="N65" s="35">
+      <c r="N65" s="36">
         <v>16.45</v>
       </c>
-      <c r="O65" s="35">
+      <c r="O65" s="36">
         <v>9.2</v>
       </c>
-      <c r="P65" s="35">
+      <c r="P65" s="36">
         <v>3.79</v>
       </c>
-      <c r="Q65" s="35">
+      <c r="Q65" s="36">
         <v>4.54</v>
       </c>
-      <c r="R65" s="35">
+      <c r="R65" s="36">
         <v>4.21</v>
       </c>
-      <c r="S65" s="35">
+      <c r="S65" s="36">
         <v>1.64</v>
       </c>
-      <c r="T65" s="35">
+      <c r="T65" s="36">
         <v>2.82</v>
       </c>
-      <c r="U65" s="35">
+      <c r="U65" s="36">
         <v>4.46</v>
       </c>
-      <c r="V65" s="35">
+      <c r="V65" s="36">
         <v>6.77</v>
       </c>
-      <c r="W65" s="35">
+      <c r="W65" s="36">
         <v>5.88</v>
       </c>
-      <c r="X65" s="35">
+      <c r="X65" s="36">
         <v>0.36</v>
       </c>
-      <c r="Y65" s="35">
+      <c r="Y65" s="36">
         <v>0.31</v>
       </c>
-      <c r="Z65" s="35">
+      <c r="Z65" s="36">
         <v>0.27</v>
       </c>
-      <c r="AA65" s="35">
+      <c r="AA65" s="36">
         <v>0.35</v>
       </c>
-      <c r="AB65" s="35">
+      <c r="AB65" s="36">
         <v>0.31</v>
       </c>
-      <c r="AC65" s="35">
+      <c r="AC65" s="36">
         <v>1.18</v>
       </c>
-      <c r="AD65" s="35">
+      <c r="AD65" s="36">
         <v>0.91</v>
       </c>
-      <c r="AE65" s="35">
+      <c r="AE65" s="36">
         <v>1.07</v>
       </c>
-      <c r="AF65" s="35">
+      <c r="AF65" s="36">
         <v>1.04</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="32" t="s">
-        <v>554</v>
-      </c>
-      <c r="B66" s="35">
+      <c r="A66" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="B66" s="36">
         <v>18.67</v>
       </c>
-      <c r="C66" s="35">
+      <c r="C66" s="36">
         <v>18.81</v>
       </c>
-      <c r="D66" s="35">
+      <c r="D66" s="36">
         <v>21.8</v>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="36">
         <v>18.1</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="36">
         <v>20.47</v>
       </c>
-      <c r="G66" s="35">
+      <c r="G66" s="36">
         <v>23.81</v>
       </c>
-      <c r="H66" s="35">
+      <c r="H66" s="36">
         <v>20.91</v>
       </c>
-      <c r="I66" s="35">
+      <c r="I66" s="36">
         <v>16.33</v>
       </c>
-      <c r="J66" s="35">
+      <c r="J66" s="36">
         <v>17.92</v>
       </c>
-      <c r="K66" s="35">
+      <c r="K66" s="36">
         <v>14.2</v>
       </c>
-      <c r="L66" s="35">
+      <c r="L66" s="36">
         <v>8.42</v>
       </c>
-      <c r="M66" s="35">
+      <c r="M66" s="36">
         <v>6.75</v>
       </c>
-      <c r="N66" s="35">
+      <c r="N66" s="36">
         <v>5.78</v>
       </c>
-      <c r="O66" s="35">
+      <c r="O66" s="36">
         <v>4.08</v>
       </c>
-      <c r="P66" s="35">
+      <c r="P66" s="36">
         <v>3.29</v>
       </c>
-      <c r="Q66" s="35">
+      <c r="Q66" s="36">
         <v>3.44</v>
       </c>
-      <c r="R66" s="35">
+      <c r="R66" s="36">
         <v>3.58</v>
       </c>
-      <c r="S66" s="35">
+      <c r="S66" s="36">
         <v>3.65</v>
       </c>
-      <c r="T66" s="35">
+      <c r="T66" s="36">
         <v>1.81</v>
       </c>
-      <c r="U66" s="35">
+      <c r="U66" s="36">
         <v>1.16</v>
       </c>
-      <c r="V66" s="35">
+      <c r="V66" s="36">
         <v>0.69</v>
       </c>
-      <c r="W66" s="35">
+      <c r="W66" s="36">
         <v>0.44</v>
       </c>
-      <c r="X66" s="35">
+      <c r="X66" s="36">
         <v>0.32</v>
       </c>
-      <c r="Y66" s="35">
+      <c r="Y66" s="36">
         <v>0.34</v>
       </c>
-      <c r="Z66" s="35">
+      <c r="Z66" s="36">
         <v>0.4</v>
       </c>
-      <c r="AA66" s="35">
+      <c r="AA66" s="36">
         <v>0.53</v>
       </c>
-      <c r="AB66" s="35">
+      <c r="AB66" s="36">
         <v>0.68</v>
       </c>
-      <c r="AC66" s="33"/>
-      <c r="AD66" s="33"/>
-      <c r="AE66" s="33"/>
-      <c r="AF66" s="33"/>
+      <c r="AC66" s="34"/>
+      <c r="AD66" s="34"/>
+      <c r="AE66" s="34"/>
+      <c r="AF66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>555</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
-      <c r="X67" s="31"/>
-      <c r="Y67" s="31"/>
-      <c r="Z67" s="31"/>
-      <c r="AA67" s="31"/>
-      <c r="AB67" s="31"/>
-      <c r="AC67" s="31"/>
-      <c r="AD67" s="31"/>
-      <c r="AE67" s="31"/>
-      <c r="AF67" s="31"/>
+      <c r="A67" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="32"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
+      <c r="W67" s="32"/>
+      <c r="X67" s="32"/>
+      <c r="Y67" s="32"/>
+      <c r="Z67" s="32"/>
+      <c r="AA67" s="32"/>
+      <c r="AB67" s="32"/>
+      <c r="AC67" s="32"/>
+      <c r="AD67" s="32"/>
+      <c r="AE67" s="32"/>
+      <c r="AF67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="32" t="s">
-        <v>556</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="33" t="s">
+        <v>557</v>
+      </c>
+      <c r="B68" s="35">
         <v>116.65</v>
       </c>
-      <c r="C68" s="35">
+      <c r="C68" s="36">
         <v>23.88</v>
       </c>
-      <c r="D68" s="33"/>
-      <c r="E68" s="33"/>
-      <c r="F68" s="35">
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="36">
         <v>4.64</v>
       </c>
-      <c r="G68" s="35">
+      <c r="G68" s="36">
         <v>32.19</v>
       </c>
-      <c r="H68" s="35">
+      <c r="H68" s="36">
         <v>24.65</v>
       </c>
-      <c r="I68" s="35">
+      <c r="I68" s="36">
         <v>9.84</v>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="36">
         <v>5.45</v>
       </c>
-      <c r="K68" s="35">
+      <c r="K68" s="36">
         <v>43.33</v>
       </c>
-      <c r="L68" s="35">
+      <c r="L68" s="36">
         <v>5.98</v>
       </c>
-      <c r="M68" s="35">
+      <c r="M68" s="36">
         <v>7.65</v>
       </c>
-      <c r="N68" s="33"/>
-      <c r="O68" s="35">
+      <c r="N68" s="34"/>
+      <c r="O68" s="36">
         <v>29.82</v>
       </c>
-      <c r="P68" s="35">
+      <c r="P68" s="36">
         <v>91.41</v>
       </c>
-      <c r="Q68" s="34">
+      <c r="Q68" s="35">
         <v>327.21</v>
       </c>
-      <c r="R68" s="35">
+      <c r="R68" s="36">
         <v>6.89</v>
       </c>
-      <c r="S68" s="35">
+      <c r="S68" s="36">
         <v>19.09</v>
       </c>
-      <c r="T68" s="35">
+      <c r="T68" s="36">
         <v>21.39</v>
       </c>
-      <c r="U68" s="33"/>
-      <c r="V68" s="35">
+      <c r="U68" s="34"/>
+      <c r="V68" s="36">
         <v>10.79</v>
       </c>
-      <c r="W68" s="35">
+      <c r="W68" s="36">
         <v>17.8</v>
       </c>
-      <c r="X68" s="35">
+      <c r="X68" s="36">
         <v>10.51</v>
       </c>
-      <c r="Y68" s="35">
+      <c r="Y68" s="36">
         <v>8.38</v>
       </c>
-      <c r="Z68" s="35">
+      <c r="Z68" s="36">
         <v>12.83</v>
       </c>
-      <c r="AA68" s="35">
+      <c r="AA68" s="36">
         <v>11.23</v>
       </c>
-      <c r="AB68" s="35">
+      <c r="AB68" s="36">
         <v>6.92</v>
       </c>
-      <c r="AC68" s="35">
+      <c r="AC68" s="36">
         <v>7.51</v>
       </c>
-      <c r="AD68" s="35">
+      <c r="AD68" s="36">
         <v>26.32</v>
       </c>
-      <c r="AE68" s="35">
+      <c r="AE68" s="36">
         <v>8.87</v>
       </c>
-      <c r="AF68" s="33"/>
+      <c r="AF68" s="34"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="32" t="s">
-        <v>557</v>
-      </c>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="35">
+      <c r="A69" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="36">
         <v>25.81</v>
       </c>
-      <c r="F69" s="35">
+      <c r="F69" s="36">
         <v>9.9</v>
       </c>
-      <c r="G69" s="35">
+      <c r="G69" s="36">
         <v>14.42</v>
       </c>
-      <c r="H69" s="35">
+      <c r="H69" s="36">
         <v>10.84</v>
       </c>
-      <c r="I69" s="35">
+      <c r="I69" s="36">
         <v>8.68</v>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="36">
         <v>13.6</v>
       </c>
-      <c r="K69" s="35">
+      <c r="K69" s="36">
         <v>21.94</v>
       </c>
-      <c r="L69" s="35">
+      <c r="L69" s="36">
         <v>23.18</v>
       </c>
-      <c r="M69" s="35">
+      <c r="M69" s="36">
         <v>56.46</v>
       </c>
-      <c r="N69" s="35">
+      <c r="N69" s="36">
         <v>37.0</v>
       </c>
-      <c r="O69" s="35">
+      <c r="O69" s="36">
         <v>21.42</v>
       </c>
-      <c r="P69" s="35">
+      <c r="P69" s="36">
         <v>19.96</v>
       </c>
-      <c r="Q69" s="35">
+      <c r="Q69" s="36">
         <v>35.94</v>
       </c>
-      <c r="R69" s="35">
+      <c r="R69" s="36">
         <v>20.9</v>
       </c>
-      <c r="S69" s="35">
+      <c r="S69" s="36">
         <v>37.36</v>
       </c>
-      <c r="T69" s="35">
+      <c r="T69" s="36">
         <v>30.66</v>
       </c>
-      <c r="U69" s="35">
+      <c r="U69" s="36">
         <v>26.99</v>
       </c>
-      <c r="V69" s="35">
+      <c r="V69" s="36">
         <v>11.44</v>
       </c>
-      <c r="W69" s="35">
+      <c r="W69" s="36">
         <v>11.75</v>
       </c>
-      <c r="X69" s="35">
+      <c r="X69" s="36">
         <v>9.69</v>
       </c>
-      <c r="Y69" s="35">
+      <c r="Y69" s="36">
         <v>9.02</v>
       </c>
-      <c r="Z69" s="35">
+      <c r="Z69" s="36">
         <v>10.51</v>
       </c>
-      <c r="AA69" s="35">
+      <c r="AA69" s="36">
         <v>9.75</v>
       </c>
-      <c r="AB69" s="35">
+      <c r="AB69" s="36">
         <v>27.21</v>
       </c>
-      <c r="AC69" s="33"/>
-      <c r="AD69" s="33"/>
-      <c r="AE69" s="33"/>
-      <c r="AF69" s="33"/>
+      <c r="AC69" s="34"/>
+      <c r="AD69" s="34"/>
+      <c r="AE69" s="34"/>
+      <c r="AF69" s="34"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>558</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="31"/>
-      <c r="T70" s="31"/>
-      <c r="U70" s="31"/>
-      <c r="V70" s="31"/>
-      <c r="W70" s="31"/>
-      <c r="X70" s="31"/>
-      <c r="Y70" s="31"/>
-      <c r="Z70" s="31"/>
-      <c r="AA70" s="31"/>
-      <c r="AB70" s="31"/>
-      <c r="AC70" s="31"/>
-      <c r="AD70" s="31"/>
-      <c r="AE70" s="31"/>
-      <c r="AF70" s="31"/>
+      <c r="A70" s="31" t="s">
+        <v>559</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
+      <c r="V70" s="32"/>
+      <c r="W70" s="32"/>
+      <c r="X70" s="32"/>
+      <c r="Y70" s="32"/>
+      <c r="Z70" s="32"/>
+      <c r="AA70" s="32"/>
+      <c r="AB70" s="32"/>
+      <c r="AC70" s="32"/>
+      <c r="AD70" s="32"/>
+      <c r="AE70" s="32"/>
+      <c r="AF70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="32" t="s">
-        <v>559</v>
-      </c>
-      <c r="B71" s="34">
+      <c r="A71" s="33" t="s">
+        <v>560</v>
+      </c>
+      <c r="B71" s="35">
         <v>151.65</v>
       </c>
-      <c r="C71" s="35">
+      <c r="C71" s="36">
         <v>27.03</v>
       </c>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="35">
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="36">
         <v>4.8</v>
       </c>
-      <c r="G71" s="35">
+      <c r="G71" s="36">
         <v>42.39</v>
       </c>
-      <c r="H71" s="35">
+      <c r="H71" s="36">
         <v>43.19</v>
       </c>
-      <c r="I71" s="35">
+      <c r="I71" s="36">
         <v>11.97</v>
       </c>
-      <c r="J71" s="35">
+      <c r="J71" s="36">
         <v>5.92</v>
       </c>
-      <c r="K71" s="35">
+      <c r="K71" s="36">
         <v>92.0</v>
       </c>
-      <c r="L71" s="35">
+      <c r="L71" s="36">
         <v>6.36</v>
       </c>
-      <c r="M71" s="35">
+      <c r="M71" s="36">
         <v>8.26</v>
       </c>
-      <c r="N71" s="33"/>
-      <c r="O71" s="35">
+      <c r="N71" s="34"/>
+      <c r="O71" s="36">
         <v>49.89</v>
       </c>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="33"/>
-      <c r="R71" s="35">
+      <c r="P71" s="34"/>
+      <c r="Q71" s="34"/>
+      <c r="R71" s="36">
         <v>7.71</v>
       </c>
-      <c r="S71" s="35">
+      <c r="S71" s="36">
         <v>89.8</v>
       </c>
-      <c r="T71" s="35">
+      <c r="T71" s="36">
         <v>36.73</v>
       </c>
-      <c r="U71" s="33"/>
-      <c r="V71" s="35">
+      <c r="U71" s="34"/>
+      <c r="V71" s="36">
         <v>12.66</v>
       </c>
-      <c r="W71" s="35">
+      <c r="W71" s="36">
         <v>30.37</v>
       </c>
-      <c r="X71" s="33"/>
-      <c r="Y71" s="35">
+      <c r="X71" s="34"/>
+      <c r="Y71" s="36">
         <v>39.18</v>
       </c>
-      <c r="Z71" s="33"/>
-      <c r="AA71" s="35">
+      <c r="Z71" s="34"/>
+      <c r="AA71" s="36">
         <v>35.67</v>
       </c>
-      <c r="AB71" s="35">
+      <c r="AB71" s="36">
         <v>14.57</v>
       </c>
-      <c r="AC71" s="35">
+      <c r="AC71" s="36">
         <v>21.73</v>
       </c>
-      <c r="AD71" s="33"/>
-      <c r="AE71" s="35">
+      <c r="AD71" s="34"/>
+      <c r="AE71" s="36">
         <v>14.25</v>
       </c>
-      <c r="AF71" s="33"/>
+      <c r="AF71" s="34"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="32" t="s">
-        <v>560</v>
-      </c>
-      <c r="B72" s="33"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="35">
+      <c r="A72" s="33" t="s">
+        <v>561</v>
+      </c>
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="36">
         <v>37.95</v>
       </c>
-      <c r="F72" s="35">
+      <c r="F72" s="36">
         <v>11.41</v>
       </c>
-      <c r="G72" s="35">
+      <c r="G72" s="36">
         <v>18.1</v>
       </c>
-      <c r="H72" s="35">
+      <c r="H72" s="36">
         <v>12.93</v>
       </c>
-      <c r="I72" s="35">
+      <c r="I72" s="36">
         <v>9.8</v>
       </c>
-      <c r="J72" s="35">
+      <c r="J72" s="36">
         <v>15.86</v>
       </c>
-      <c r="K72" s="35">
+      <c r="K72" s="36">
         <v>28.61</v>
       </c>
-      <c r="L72" s="35">
+      <c r="L72" s="36">
         <v>33.21</v>
       </c>
-      <c r="M72" s="34">
+      <c r="M72" s="35">
         <v>229.95</v>
       </c>
-      <c r="N72" s="35">
+      <c r="N72" s="36">
         <v>78.18</v>
       </c>
-      <c r="O72" s="35">
+      <c r="O72" s="36">
         <v>35.69</v>
       </c>
-      <c r="P72" s="35">
+      <c r="P72" s="36">
         <v>33.43</v>
       </c>
-      <c r="Q72" s="34">
+      <c r="Q72" s="35">
         <v>105.88</v>
       </c>
-      <c r="R72" s="35">
+      <c r="R72" s="36">
         <v>34.5</v>
       </c>
-      <c r="S72" s="34">
+      <c r="S72" s="35">
         <v>152.33</v>
       </c>
-      <c r="T72" s="33"/>
-      <c r="U72" s="33"/>
-      <c r="V72" s="34">
+      <c r="T72" s="34"/>
+      <c r="U72" s="34"/>
+      <c r="V72" s="35">
         <v>143.05</v>
       </c>
-      <c r="W72" s="33"/>
-      <c r="X72" s="33"/>
-      <c r="Y72" s="35">
+      <c r="W72" s="34"/>
+      <c r="X72" s="34"/>
+      <c r="Y72" s="36">
         <v>47.34</v>
       </c>
-      <c r="Z72" s="35">
+      <c r="Z72" s="36">
         <v>88.8</v>
       </c>
-      <c r="AA72" s="35">
+      <c r="AA72" s="36">
         <v>27.06</v>
       </c>
-      <c r="AB72" s="33"/>
-      <c r="AC72" s="33"/>
-      <c r="AD72" s="33"/>
-      <c r="AE72" s="33"/>
-      <c r="AF72" s="33"/>
+      <c r="AB72" s="34"/>
+      <c r="AC72" s="34"/>
+      <c r="AD72" s="34"/>
+      <c r="AE72" s="34"/>
+      <c r="AF72" s="34"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
